--- a/report.xlsx
+++ b/report.xlsx
@@ -543,13 +543,9 @@
         <v>20</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>โรงแรมขนาดกลางที่ตั้งอยู่ริมหาดบางเกตุ ซึ่งเป็นหาดที่ทอดตัวยาวต่อมามาจากชายหาดชะอำ ตัวโรงแรมจะมีห้องพักหลายประเภท แบบเริ่มต้น ห้องใหญ่ ห้องริมสระน้ำ ซึ่งบางห้องอาจจะเห็นวิวทะเล แต่ส่วนใหญ่จะเป็นลักษณะ</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -602,12 +598,16 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>โรงแรมเก่า แต่สะอาด ห้องสวย บรรยากาศดี บริการดี มีรถกอล์ฟส่งถึงล็อบบี้ มี เบลบอย ยกของขึ้นห้องให้ โลเคชั่นก็ดีมากใจกลางเมือง ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -634,13 +634,9 @@
         <v>172</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>เราจองให้พี่สาวแต่ไม่ได้พัก เข้าไปที่พักเก่าไม่พอ ไม่สอาดอีก บรรยากาศข้างนอกดูแบบว่าเหมือนไม่มีใครอยู่ พอเดินเข้าไปในห้องเหมือนไม่ได้ทำความสะอาดมีฝุ่นเกาะ ทุกอย่างเก่าหมด ตั้งแต่ลานจอดรถห้องอาหารถึงห้</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -693,14 +689,14 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">โรงแรมเก่าแต่ปรับปรุงแล้วก็ดูดีพอสมควร  ใหญ่มาก ทำให้เดินไกลมาก  สระน้ำใหญ่ เล่นสนุก  อาหารเช้า พอรองท้องได้ แต่พนง ตึงมาก ไม่มีเซอร์วิสมายด์  ห้องประชุมดีนะ ขนาดกำลังดีสำหรับจัดงาน แอร์เย็นน้อยไปนิด </t>
+          <t>เข้าพักที่นี่สองคืน เป็นโรงแรมใหญ่ที่มีมีอายุ พนักงานบริการดี ไลน์อาหารบุฟเฟ่ต์ตอนเช้ามีเยอะ แอร์ยังเป็นระบบฝังฝ้าแบบเก่า ห้องที่ได้แอร์ไม่ค่อยเย็น ช่วงที่เข้าพักมีโปรโมชั่นได้คูปองแลกอาหารเครื่องดื่ม</t>
         </is>
       </c>
     </row>
@@ -889,7 +885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -902,7 +898,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>รอบนี้ (2026-06-29 14:54) มีรีวิวใหม่ 22 รายการ | เทียบรอบก่อน 2026-06-25 02:50</t>
+          <t>รอบนี้ (2026-07-06 14:17) มีรีวิวใหม่ 3 รายการ | เทียบรอบก่อน 2026-06-29 14:54</t>
         </is>
       </c>
     </row>
@@ -936,23 +932,23 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>IMC</t>
+          <t>IPL</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Imperial Chiang Mai Resort and Sport Club</t>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nuttarika Plasuwan</t>
+          <t>Duangruthai PT</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>เราจองให้พี่สาวแต่ไม่ได้พัก เข้าไปที่พักเก่าไม่พอ ไม่สอาดอีก บรรยากาศข้างนอกดูแบบว่าเหมือนไม่มีใครอยู่ พอเดินเข้าไปในห้องเหมือนไม่ได้ทำความสะอาดมีฝุ่นเกาะ ทุกอย่างเก่าหมด ตั้งแต่ลานจอดรถห้องอาหารถึงห้องพักในราคา8ร้อยคิดว่าไม่คุ้มเลย บรรยากาศตอนกลางคืนน่ากลัว คืนนั้นเลยไม่ได้เข้าพัก ควรปรับปรุงค่ะถ้าจะขายราคานี้ แล้วในรูปตอนจองสวยมาก</t>
+          <t>เข้าพักที่นี่สองคืน เป็นโรงแรมใหญ่ที่มีมีอายุ พนักงานบริการดี ไลน์อาหารบุฟเฟ่ต์ตอนเช้ามีเยอะ แอร์ยังเป็นระบบฝังฝ้าแบบเก่า ห้องที่ได้แอร์ไม่ค่อยเย็น ช่วงที่เข้าพักมีโปรโมชั่นได้คูปองแลกอาหารเครื่องดื่มได้ด้วย ราคาคุ้มค่าเหมาะสมกับการพักผ่อนค่ะ ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 4 บริการ: 5 สถานที่ตั้ง: 4 ไฮไลต์ของโรงแรม หรูหรา วิวสวย เงียบสงบ และ คุ้มค่า</t>
         </is>
       </c>
     </row>
@@ -969,473 +965,36 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7ackie Srichompan</t>
+          <t>natthapong jitsai</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>โรงแรมเก่าแต่ปรับปรุงแล้วก็ดูดีพอสมควร  ใหญ่มาก ทำให้เดินไกลมาก  สระน้ำใหญ่ เล่นสนุก  อาหารเช้า พอรองท้องได้ แต่พนง ตึงมาก ไม่มีเซอร์วิสมายด์  ห้องประชุมดีนะ ขนาดกำลังดีสำหรับจัดงาน แอร์เย็นน้อยไปนิด  น้ำแรง น้ำอุ่น แอร์เย็น ห้องมืดสลัวไปหน่อย บางห้องเป็นดูเพล็ก (มี 2 ชั้น)  ภาพรวมก็พักได้ครับ ห้องพัก: 3 บริการ: 3 สถานที่ตั้ง: 4</t>
+          <t>เท่าที่เห็น สระว่ายน้ำ ที่นี้ สวยที่สุดครับ กว้างขวางมากๆ วิวดี น้ำใส่สะอาด ครับ น่ามาเล่นมากๆ ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม วิวสวย เงียบสงบ และ คุ้มค่า</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>IBC</t>
+          <t>IMK</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
+          <t>Imperial Hotel Convention Center Korat</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>pakinai kasiwat</t>
+          <t>Thammatorn Kraikokit</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>โรงแรมขนาดกลางที่ตั้งอยู่ริมหาดบางเกตุ ซึ่งเป็นหาดที่ทอดตัวยาวต่อมามาจากชายหาดชะอำ ตัวโรงแรมจะมีห้องพักหลายประเภท แบบเริ่มต้น ห้องใหญ่ ห้องริมสระน้ำ ซึ่งบางห้องอาจจะเห็นวิวทะเล แต่ส่วนใหญ่จะเป็นลักษณะของห้องที่หันหน้าเข้ากันมากกว่า ภายในโรงแรมมีสระว่ายน้ำริมทะเลขนาดเล็ก ห้องฟิตเนส และอาหารเช้าให้บริการแก่ผู้เข้าพัก สามารถจอดรถได้ที่ลานจอดรถกลางแจ้งด้านหน้าที่พัก  วันที่เข้าใช้บริการเป็นช่วงคืนวันศุกร์ ตอนกลางกลางเดือนมกราคม ได้จองเข้ามากับที่พักเป็นแบบกรุ๊ปทัวร์ ลูกค้าในโรงแรมค่อนข้างบางตาในวันนี้ ได้ห้องพักเป็นแบบห้องเริ่มต้นชั้นสี่ เกือบริมสุด จึงทำให้เห็นทะเลได้จากระเบียงห้องพักบางส่วน ภายในห้องมีสิ่งอำนวยความสะดวกครบครัน มีทั้งทีวีขนาดใหญ่  โซฟา กาน้ำร้อน ตู้เย็น ไดเป่าผม เครื่องทำน้ำอุ่นเป็นต้น ขนาดห้องใหญ่พอสมควร พร้อมอาหารเช้า  โดยรวมแล้ว เป็นโรงแรมที่ค่อนข้างเงียบสงบ เนื่องจากบริเวณโดยรอบตลอดแนวชายหาดนั้นยังไม่ค่อยมีโรงแรมเจ้าอื่นมาเปิดให้บริการเท่าไหร่ ความสะอาดของตัวชายหาดและน้ำทะเลหน้าหาดอยู่ในเกณฑ์พอรับได้ อาหารเช้าของทางโรงแรมโดยส่วนตัวยังรู้สึกว่าเมนูไม่ได้หลากหลายเท่าที่ควร ห้องพักที่ให้บริการทำออกมาได้ดี ห้องฟิตเนสมีเครื่องเล่นให้ทั้ง เวทเทรนนิ่งและคาร์ดิโอเยอะใช้ได้ แต่บันไดลงหาดมีขนาดเล็กและชัน ค่อนข้างอันตรายต่อผู้สูงอายุ หาดบางเกตุ ห้องน้ำที่ให้ให้บริการในส่วนของห้องประชุมสัมมนานั้นเล็กมาก เมื่อเข้าใช้บริการพร้อมกันต้องเสียเวลารอนาน ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 4 บริการ: 3 สถานที่ตั้ง: 3 ไฮไลต์ของโรงแรม เงียบสงบ</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>IBC</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>phraophitcha</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>หาดบางเกตุ เพรชบุรี เงียบสงบ สะอาด หาดชายกว้างโล่งมองแล้วสบายตา ชอบตรงคนไม่เยอะไม่วุ่นวาย โรงแรมที่พักติดกับหาดมีความเป็นส่วนตัว อาหารก็ดีเลยจัดเต็มเหมาะสมกับราคา พนักงาน ต้อนรับยิ้มแย้ม พร้อมให้ความช่วยเหลือ ทั่งหาดน่าจะมีแค่7-11 แค่สาขาเดียว เลิศมาก รับรองไปอีกแน่นอน เสียดายคือไปช่วงมีฝนเลยชื้นไปทุกที</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>IBC</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>walunon Chookaew</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>ไม่ตรงปกมากๆค่ะ อาหารไม่อร่อย ปลาหมึกแข็งเหมือนหนังยาง  ไม่สด ห้องพักแย่สุดๆ ไม่ตรงปก มีขี้นกเยอะมาก รอบๆ สระว่ายน้ำก็สกปรก มีขวดเบียร์วางเต็มพื้น เศษขยะเยอะ ไม่สะอาดมากๆ สระว่ายน้ำเล็กมากๆ การบริการของพนักงานก็ไม่ดีค่ะ  ค่าห้องแพงไม่สมราคาเลยจริงๆ ประเภทการเดินทาง วันหยุดพักผ่อน ห้องพัก: 1 บริการ: 1 สถานที่ตั้ง: 1 ห้องพัก แย่มากๆ สกปรก ขี้นกเยอะ มุมห้องเห็นสถานที่ก่อสร้าง ไม่เข้าใจเรื่องเตียงเดี่ยว เตียงคู่ แนกแยะไม่ออก กิจกรรมในบริเวณใกล้เคียง ไม่มี ได้ยินเสียงก่อสร้าง อาหารและเครื่องดื่ม อาหารไม่อร่อย ไม่สด ปลาหมึกแข็งเหมือนหนังยาง ผักแข็ง รสชาติอาหารแย่มากๆ รายละเอียดที่น่าสนใจ ไม่มี คงไม่ไปอีกต่อไปแล้วค่ะ</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>IBC</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Wip Pattatesang</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>ห้องพัก จัดวางได้ดีแต่ห้องมีกลิ่นอับชื้น  คุณลุงรปภ.ทำงานใส่ใจยริการมาก โรงแรมติดทะเล แต่ไม่เหมาะกับ คนที่สูบบุหรี่ เนื่องจากระเบียงห้ามสูบ อยากให้แนะนำแจ้งเงื่อนไขในplatform ด้วย ห้องพัก: 4 บริการ: 3 สถานที่ตั้ง: 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>IBC</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Phimphisa Muadchan</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr"/>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>🏨location โรงแรมไม่ได้อยู่ชะอำจ๋า ค่อนมาก่อนถึงชะอำ โรงแรมอยู่ติดหาดเลย หน้าหาดรร.ไม่กว้างมาก บรรยากาศดี หาดทรายสะอาด เล่นน้ำได้ แต่ตอนไปไปช่วงเทศกาล คนเยอะมาก ส่วนใหญ่แขกที่มาพักจะเป็นครอบครัวเสียส่วนใหญ่ สระว่ายน้ำส่วนกลางเล็ก คนเยอะ เด็กเล่นกันเต็มสระ เก้าอี้ริมหาดมีน้อย ไม่พอจะนั่ง + สกปรก มีทั้งขยะที่คนก่อนๆกินไว้ เปียก ไม่มีพนง.ดูแลส่วนกลางริมหาดและสระว่ายน้ำ 🚪ห้องที่จองเป็น pool access ตึกB request ห้องไปทางรร.ก็จัดให้ตามที่ขอ สระตึกBค่อนข้างกว้างและเป็นส่วนตัวกว่าตึก A อยู่นิดหน่อย น้ำสระสะอาด ห้องกว้างขวาง แอร์เย็นฉ่ำ น้ำแรงดี เตียงนอนสบาย ห้องสะอาดในระดับนึง amentity มีcotton bud กะหมวกคลุมผม มีรองเท้าแตะ ร่ม น้ำ2ขวด ไดร์เป่าผม ถือว่าครยอยู่ แต่ไปช่วงเทศกาลอาจจะขาดๆเกินๆไปบ้าง ผ้าเช็ดตัวและผ้าเช็ดเท้าไม่พร้อมมีให้ตอนเช็คอิน เอามาวางไว้ให้ในห้องทั้งๆที่แขวน do not disturb ที่ประตูไว้ แต่ไม่มีอะไรหาย ปลอกหมอนก็ลืมใส่ให้ แต่เห็นตอนจะนอนแล้วเลยไม่ได้แจ้งรร. อาจจะขรุขระช่วงเทศกาล คนเยอะ ซักไม่ทัน แม่บ้านอาจจะรีบ 🍚อาหารเช้าโอเค มีไม่ค่อยเยอะ แต่ก็มีทั้งไทย ฝรั่ง ข้าวต้ม ก๋วยเตี๋ยว 😊โรงแรมมีใส่บาตรตอนเช้าทุกวัน เตรียมเองหรือให้รร.เตรียมให้ก็ได้ ชุดละ 200 พนง.น่ารัก เป็นกันเอง อาจจะดูแลไม่ทั่วถึงไปบ้าง แต่เข้าใจได้ค่ะ ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว คู่รัก ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 4 ไฮไลต์ของโรงแรม วิวสวย</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>IBC</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>วัชรี ธนะรุ่ง</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr"/>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>พนักงานน่ารักมากค่ะ บรรยากาศดี ไม่วุ่นวาย สระว่ายน้ำสะอาด ห้องพักน่ารักมากๆเลยค่ะ ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>IBC</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Maxs Tns</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr"/>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>โรงแรมนอนสบาย แต่แนะนำหาข้าวมากินด้วยเพราะจืดไม่มีรสชาติเหมือนไม่มีเครื่องปรุง แต่พอมากินตอนเช้าที่รวมกับกรุ้ปทัวรฺอื่น อร่อยซะงั้น(แปลกป่ะ😂😂) สุด จัดกิจกรรมโต๊ะจีนชั้น 2 ให้แค่ 4 ทุ่ม แต่คนมาข้างล่าง ให้ถึง เที่ยงคืน แนะนำถ้าอยากได้นั่งยาวๆพกตังไปครับ ขอซื้อโซดา น้ำแข็ง ไล่ให้ไปซื้อ เซเว่น บอกไม่มี แต่คนอื่นแจกช้ำ รู้สึกเหมือนขอทานมาก</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>IBC</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Jackie Paponnat</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr"/>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>เปิดประตูหลังห้องมา เจอสระว่ายน้ำเลย มีความเป็นส่วนตัว สระส่วนกลางติดหาดมองเห็นวิวทะเล ถ่ายรูปสวย เหมาะกับการพักผ่อน ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว อาหารและเครื่องดื่ม อาหารอร่อย แต่ราคาค่อนข้างสูง หากเรามองที่คุณภาพ ราคานี้ถือว่ายังได้อยู่ รายละเอียดที่น่าสนใจ ถ้ายังไม่เคยมา ลองมาเที่ยวกันดู จะได้รู้ รู้ด้วยตนเองดีที่สุดครับผม ไฮไลต์ของโรงแรม วิวสวย โรแมนติก และ เงียบสงบ</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>IBC</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Davika Polnyoong</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr"/>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>ไปเที่ยวสัมมนากับที่ทำงาน รู้สึกไม่ประทับใจเลย ห้องพักก็พอได้แต่ห้องน้ำท่อตันนะคะ คืออาบน้ำแล้วน้ำท่วม ส่วนการจัดเลี้ยงชั้น2 อาหารคือแบบทานไม่ได้เลยคะ ไม่แน่ใจว่าตั้งใจทำให้ไม่อร่อยไหม เพราะอาหารเช้าที่ทานรวมกับกรุ๊ปทัวร์อื่นคืออร่อย ส่วนห้องจัดเลี้ยงได้แค่ 4 ทุ่ม ลงมาหน้าหน้าโรงแรมด้านล่าง ก็รู้สึกไม่โอเคเราก็นั่งแบบชิวๆเลย จนกระทั่ง ตี 2 กว่า ดับไฟซึ่งงมากไม่มีเจ้าหน้าที่มาแจ้งเลยคิดจะดับไฟก็ดับ ไม่มีความประทับใจเลยคะ คิดว่าจะพาครอบครัวมาซ้ำเจอแบบนี้ไม่ซ้ำแล้วคะ ขอซื้อน้ำแข็งโชดาเพิ่มช้ามาก เหมือนเราเป็นขอทาน 🥺 จบการรีวิวคะ ห้องพัก: 1 บริการ: 1 สถานที่ตั้ง: 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>IBC</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Wanatthaphong th</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr"/>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>มีหาดส่วนตัว ชายหาดสะอาด เป็นส่วนตัว กว้างบรรยากาศดี เงียบสงบ เหมาะสำหรับพักผ่อน สำหรับคู่รักหรือครอบครัว ที่ชอบความเป็นส่วนตัว ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ห้องพัก ห้องพักอุปกรณ์อำนวยความสะดวกครบครัน แอร์เย็นสบาย ห้องน้ำสะอาด ไฟส่องสว่างดี มีวิวดูทะเลแทบแทบจะทุกห้อง กิจกรรมในบริเวณใกล้เคียง ส่วนมากจะเป็น โรงแรมส่วนตัว ความปลอดภัย มีรปภ. รักษาความปลอดภัยและพนักงานต้อนรับ ทั้งโรงอาหาร บริเวณอาหารหน้าริมหาด และห้องรีเซฟชั่น ของห้องต้อนรับ ความสามารถเดินได้ สามารถเดินออกไปที่ชายหาดส่วนตัวได้ง่ายง่าย เพราะโรงแรมตั้งอยู่ที่หน้าหาดส่วนตัวเลย เดินลงหาดได้เลย อาหารและเครื่องดื่ม มีอาหารเช้า ตั้งแต่ 7 โมงเช้าถึง 11 โมงเช้า รายละเอียดที่น่าสนใจ ที่พักที่ ให้ความเป็นส่วนตัว ในระดับราคาที่ไม่ได้สูงเกินไป มีสระว่ายน้ำของโรงแรมส่วนตัว มีที่ล้างตัวสะอาดน้ำจืด ที่พักชั้นหนึ่งหรือชั้นที่อยู่บนพื้นดิน มีห้องว่ายน้ำส่วนตัวหน้าห้อง หรือบริเวณข้างห้อง ซึ่งเจ้าของห้องที่พักชั้นหนึ่ง สามารถที่จะว่ายน้ำที่บริเวณห้องของตัวเองได้เลย ส่วนห้องที่อยู่ข้างบนชั้นสองสามขึ้นไป ก็จะจะมีสระว่ายน้ำอยู่หน้าหาดหาดหาด เหมาะกับและเด็ก ไฮไลต์ของโรงแรม หรูหรา วิวสวย โรแมนติก เงียบสงบ เหมาะสำหรับเด็ก และ คุ้มค่า</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>IBC</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Nattinun Pitakphothakul</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr"/>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>เช็คอิน 14:00 มา 14:00 น. ต้องนั่งรอห้องอีก 1 ชั่วโมงกว่า เพราะว่าห้องยังทำความสะอาดไม่เรียบร้อย ครั้งแรกและครั้งสุดท้ายค่ะ แนะนำไปที่อื่นๆดีกว่าค่ะ การจัดการแย่มากค่ะ เสียเวลาต้องมานั่งรอ แทนที่จะได้พักผ่อนค่ะ 👎🏻👎🏻👎🏻 ห้องพัก: 1 บริการ: 1 สถานที่ตั้ง: 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>IBC</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Montree Tripetpisai</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr"/>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>ผมมีโอกาสไปร่วมกิจกรรมของกรมส่งเสริมอุตสาหกรรม ในโครงการ DIPROM Young SMEs Network #3  ซึ่งเป็นกิจกรรมที่รวมเอาทายาทธุรกิจที่มีศักยภาพ มาทำความรู้จักและช่วยเหลือซึ่งกันและกัน  แม้ว่าตัวเองจะไปร่วมงานได้ไม่นาน แต่ก็ได้ช่วยบันทึกภาพถ่ายทางอากาศจากโดรนร่วมกับผู้เข้าอบรมและทีมผู้จัดงาน  ถือเป็นหนึ่งกิจกรรมดีๆ จากกรมส่งเสริมอุตสาหกรรม ที่จัดมาอย่างต่อเนื่องครับ ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ความปลอดภัย Yes อาหารและเครื่องดื่ม Delicious ไฮไลต์ของโรงแรม เงียบสงบ และ คุ้มค่า</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>IBC</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Karin Lisani</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr"/>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>บริการประทับใจ ห้องพักสวยที่นอนสบาย ส่วนห้องน้ำสะอาดมาก เครื่องทำน้ำอุ่นดี อาหารก็ถือว่าอร่อยเลย ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>IBC</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>yanapon kuttasingkee</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr"/>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>ห้องพักจัดสัดส่วนได้ดี มีโซฟา มีโต๊ะทำงาน ห้องน้ำเล็กไปหน่อย วิวติดทะเลดีมาก ลมดี หาดสวยดี ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม วิวสวย</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>IBC</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Jaiko Joy</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr"/>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>โรงแรมที่เน้นความเป็น ECO แบบจ๋าๆเลยนะคะที่นี่ ไฟโซลาร์จะติดตอนที่เราเดินผ่าน เจ๋งเลย วันที่เข้าพักไม่ค่อยมีคนไปพักเพราะไม่ใช่วันหยุดยาว ดีที่สุดเลย สงบ โคตรจะ PRIVATE เล่นสระว่ายน้ำได้อย่างอิสระเหมือนพื้นที่ส่วนตัว เหมือนเอาตัวเองออกจากโลกที่วุ่นวายได้พักนึงก่อนจะต้องกลับมาสู้ต่อ ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 4 ห้องพัก สะอาดดีนะคะ กิจกรรมในบริเวณใกล้เคียง มีสระว่ายน้ำ สำหรับเด็ก ไม่ลึก และของผู้ใหญ่ลึกอยู่เหมือนกัน ความปลอดภัย ปลอดภัยดีนะคะ ไม่มืด แต่คนสูงอายุอาจจะต้องจูงบ้าง ความสามารถเดินได้ เดินเล่นได้สบายๆ อาหารและเครื่องดื่ม อาหารเช้ายังไม่ค่อยเยอะเท่าไหร่ รายละเอียดที่น่าสนใจ ที่พักสงบ ส่วนตัวดี แสงตอนเย็นสวยมาก เหมาะกะการถ่ายรูปเล่นมากก ไฮไลต์ของโรงแรม วิวสวย เงียบสงบ เหมาะสำหรับเด็ก และ คุ้มค่า</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>IBC</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Kantima Jontapa</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr"/>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>อาหารแพงมาก ไม่อร่อยไม่สมราคา บางอย่างก็หวานมาก เค็มมาก ไปเป็นกรุ้ปเหมาค่าอาหารเป็นบุฟเฟต์ต่อหัว ไม่สมราคา ใช้ปลาหมึกเกรดต่ำ จริงๆถ้าทำอาหารธรรมดาๆให้อร่อยก็ไม่แปลก แต่นี่แทบกินไม่ได้ แย่มาก แต่พนักงานบริการดี</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>IBC</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Kannika Sis</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr"/>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>พึ่งไปห้องก็ดีห้องกว้าง แต่แอร์ไม่ค่อยเย็น ช่วงที่ไปมีกรุ๊ปมาคนเยอะเปิดเพลงเสียงดัง คือต้องการไปพักผ่อนกลับไม่ค่อยมีความเป็นส่วนตัวเลย ลูกจะเล่นน้ำคนก็เต็มสระไปหมด กลุ่มท่องเที่ยว ครอบครัว</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>IBC</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Parin Srisukjaisamran</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr"/>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>ห้องพักราคาดีค่ะ มาใช้บริการ วันศุกร์ คนไม่พลุกพล่าน เหมาะกับการพักผ่อนจริง ๆ ห้องพักสะอาด พนักงาน น่ารัก ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ห้องพัก พักแบบห้อง Family 2 นอน สะดวกสบายดีค่ะ แอร์เย็นเตียงนุ่ม กิจกรรมในบริเวณใกล้เคียง มีอุปกรณ์กี่ฬาทางน้ำ ให้เล่น (มีค่าใช้จ่าย) สระว่ายน้ำ ฟิตเนส หาดส่วนตัว ความปลอดภัย ดูรวม ๆ ดีค่ะ ความสามารถเดินได้ มีหาดให้เดินเล่น อาหารและเครื่องดื่ม อาหาร ตาม ราคาที่ไม่สูงมาก ก็ครบนะคะ มีหลายอย่าง แต่ฝากนิดนึง หาก ผู้บริหาร มาอ่านนะคะ ข้าวต้มหมู ควนเป็น ก้อน มากกว่า จะดูน่ากิน ผัก เครื่องเคียง ของข้าวต้ม ควรมีอะไรปิด หรือวางให้ไกลแดด เพราะแห้ง ไม่น่ากินค่ะ แต่รสชาติดีนะคะ ผัดผักกาดขาว หั่นผักเล็กเกินไป ทำให้ดูเหมือนเละ ๆ ไข่ดาวเบรคฟัดส์ ไข่แดงไม่สุกแต่ดันแห้ง อีกรายการนึง ที่ควรปรับด่วน กาแฟสดค่ะ ไม่รวมใน ไลน์อาหารเช้านะคะ ชำระเงิน สั่งลาเต้ร้อน แต่สิ่งที่ได้มา คือ น่าจะเป็นอเมริกาโน่ ใส่นม มาพอที่แก้วจะใส่ได้ ค่ะ รายละเอียดที่น่าสนใจ ก็แนะนำอยู่นะคะ หากต้องการความสงบ เพื่อพักผ่อน ไฮไลต์ของโรงแรม วิวสวย โรแมนติก เงียบสงบ เหมาะสำหรับเด็ก และ คุ้มค่า</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>IBC</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Nakarate Inthana</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr"/>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>ห้องพักดี สะอาด เตียงนอนสบายแต่ไม่มีหมอนกอดให้ บรรยากาศเงียบสงบเหมาะมาพักผ่อนมาก ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>IBC</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>paieasy sukonramuk</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr"/>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>เพิ่งไปมาเองจ้า ดีอย่างเดียวคือพนักงาน พูดจาดี ที่เหลือ ผ้าเช็ดตัวก็ไม่มีโทรไปถามบอกผ้าแห้งไม่ทันจ้า เช็คอิน 14.00 เข้าจริง14.45 ทำไมไม่ปรับเวลาเป็นเช็คอิน15.00เลยละครับห่วยสุดๆ ครั้งแรกแหละครั้งเดียว ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 1 บริการ: 5 สถานที่ตั้ง: 3</t>
+          <t>โรงแรมเก่า แต่สะอาด ห้องสวย บรรยากาศดี บริการดี มีรถกอล์ฟส่งถึงล็อบบี้ มี เบลบอย ยกของขึ้นห้องให้ โลเคชั่นก็ดีมากใจกลางเมือง ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3058,6 +2617,46 @@
         <v>1</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>IMK</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Korat</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>IPL</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/report.xlsx
+++ b/report.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -521,17 +521,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>IBC</t>
+          <t>RWK</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
+          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Petchaburi</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -540,12 +540,16 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>ประทับใจในการบริการของเจ้าหน้าที่ทุกท่าน  มืออาชีพ  ห้องพักนอนสบาย    พนักงานทุกคนยิ้มแย้มแจ่มใส ชอบมากที่สุด กับบรรยากาศที่สุดแสนจะโรแมนติก  ฟิลธรรมชาติ  ต้นไม้กางปีกอย่างร่มรื่นสุด ให้5ดาวเลยค่ะ ห้อ</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -601,13 +605,9 @@
         <v>168</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>โรงแรมเก่า แต่สะอาด ห้องสวย บรรยากาศดี บริการดี มีรถกอล์ฟส่งถึงล็อบบี้ มี เบลบอย ยกของขึ้นห้องให้ โลเคชั่นก็ดีมากใจกลางเมือง ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -692,13 +692,9 @@
         <v>169</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>เข้าพักที่นี่สองคืน เป็นโรงแรมใหญ่ที่มีมีอายุ พนักงานบริการดี ไลน์อาหารบุฟเฟ่ต์ตอนเช้ามีเยอะ แอร์ยังเป็นระบบฝังฝ้าแบบเก่า ห้องที่ได้แอร์ไม่ค่อยเย็น ช่วงที่เข้าพักมีโปรโมชั่นได้คูปองแลกอาหารเครื่องดื่ม</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -873,6 +869,31 @@
         <v>0</v>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>IBC</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Beachfront Resort Cha-am</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Petchaburi</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -885,7 +906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -898,7 +919,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>รอบนี้ (2026-07-06 14:17) มีรีวิวใหม่ 3 รายการ | เทียบรอบก่อน 2026-06-29 14:54</t>
+          <t>รอบนี้ (2026-07-13 04:32) มีรีวิวใหม่ 5 รายการ | เทียบรอบก่อน 2026-07-06 14:17</t>
         </is>
       </c>
     </row>
@@ -932,69 +953,115 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>IPL</t>
+          <t>RWK</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Imperial Hotel Convention Center Phitsanulok</t>
+          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Duangruthai PT</t>
+          <t>pattamarat thongmar</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>เข้าพักที่นี่สองคืน เป็นโรงแรมใหญ่ที่มีมีอายุ พนักงานบริการดี ไลน์อาหารบุฟเฟ่ต์ตอนเช้ามีเยอะ แอร์ยังเป็นระบบฝังฝ้าแบบเก่า ห้องที่ได้แอร์ไม่ค่อยเย็น ช่วงที่เข้าพักมีโปรโมชั่นได้คูปองแลกอาหารเครื่องดื่มได้ด้วย ราคาคุ้มค่าเหมาะสมกับการพักผ่อนค่ะ ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 4 บริการ: 5 สถานที่ตั้ง: 4 ไฮไลต์ของโรงแรม หรูหรา วิวสวย เงียบสงบ และ คุ้มค่า</t>
+          <t>ประทับใจในการบริการของเจ้าหน้าที่ทุกท่าน  มืออาชีพ  ห้องพักนอนสบาย    พนักงานทุกคนยิ้มแย้มแจ่มใส ชอบมากที่สุด กับบรรยากาศที่สุดแสนจะโรแมนติก  ฟิลธรรมชาติ  ต้นไม้กางปีกอย่างร่มรื่นสุด ให้5ดาวเลยค่ะ ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>IPL</t>
+          <t>RWK</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Imperial Hotel Convention Center Phitsanulok</t>
+          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>natthapong jitsai</t>
+          <t>Sakontorn Udomsalee</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>เท่าที่เห็น สระว่ายน้ำ ที่นี้ สวยที่สุดครับ กว้างขวางมากๆ วิวดี น้ำใส่สะอาด ครับ น่ามาเล่นมากๆ ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม วิวสวย เงียบสงบ และ คุ้มค่า</t>
+          <t>เป็นสถานที่ hidden gem ใน Bangkok เลยก็ว่าได้ หากใครต้องการหลีกความวุ่นวาย มาพักผ่อน ฮีลใจ ที่นี่ก็เป็นทางเลือกหนึ่ง บรรยากาศสงบ และที่สำคัญคืออาหารอร่อย ได้รสชาติไทยจริงๆ ได้ทาน isan set มีแกงอ่อม ลาบ ส้มตำ ไก่ทอด น้ำพริกปลาร้า ไส้กรอกอีสาน ทานจนหมดเลย ชอบน้ำพริกปลาร้ามากๆ ทานมาหลายที่แล้ว แต่ที่นี่ทำอร่อยกว่าที่อื่นมาก  ที่นี่มี สปา นวดไทย และนวดน้ำมัน ด้วย เนื่องจากจุดประสงค์ครั้งนี้คือ ผ่อนคลายความเครียด เลยเลือกนวดน้ำมัน หมอนวดคือ คุณหมอมีนา และปรียา ช่วยแนะนำและนวดให้ กล้ามเนื้อที่ตึงๆจากการทำงาน เลยเบาขึ้น แถมยังผ่อนคลายความเหนื่อยล้าได้ดีอีกด้วย ถือว่ารักษากายใจ ก่อนเริ่มงานต่อไป ได้เลิศๆ ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว คู่รัก ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม เงียบสงบ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>IMK</t>
+          <t>RWK</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Imperial Hotel Convention Center Korat</t>
+          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Thammatorn Kraikokit</t>
+          <t>LiNGEX</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>โรงแรมเก่า แต่สะอาด ห้องสวย บรรยากาศดี บริการดี มีรถกอล์ฟส่งถึงล็อบบี้ มี เบลบอย ยกของขึ้นห้องให้ โลเคชั่นก็ดีมากใจกลางเมือง ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+          <t>เป็นโรงแรมทีมีมีสวนที่สวยและน่าทึ่ง อะเมซอนในกรุงเทพ บรรยากาศเงียบสงบ เหมาะแก่การพักผ่อน อาหารไทยรสชาติดี พนักงานน่ารักทุกคน โดยเฉพาะน้องๆรีเซฟชั่น ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>RWK</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Ratchanee Ritthidej</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>พนักงานบริการใส่ใจดีมาก ห้องพักสวยมี detail และเอกลักษณ์มาก บรรยากาศร่มรื่น อาหารเช้าเป็นบุฟเฟต์อร่อย สะอาด ต้นไม้เยอะมากค่ะ ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>RWK</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>สาธิดา อุ้มญาติ</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>บรรยากาศดีมากเลยค่ะ อาหารอร่อยมากเลยค่ะปกติไม่ทานอาหารโบราณนะคะแต่มาทานที่นี่อาหารอร่อยมากเลยค่ะ ติดใจเลย ได้ลองใช้บริการสปาดู พนักงานนวดสปาก็ดีมากเลยค่ะ ทุกอย่างดูสะอาด ภาพรวมโอเคมากเลยค่ะ กลับมาอีกแน่นอน เต็มสิบไม่หักก 💯 ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม วิวสวย เงียบสงบ และ คุ้มค่า</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2657,6 +2724,26 @@
         <v>2</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>RWK</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/report.xlsx
+++ b/report.xlsx
@@ -521,17 +521,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>RWK</t>
+          <t>IBC</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
+          <t>Imperial Beachfront Resort Cha-am</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Petchaburi</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -540,40 +540,36 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>ประทับใจในการบริการของเจ้าหน้าที่ทุกท่าน  มืออาชีพ  ห้องพักนอนสบาย    พนักงานทุกคนยิ้มแย้มแจ่มใส ชอบมากที่สุด กับบรรยากาศที่สุดแสนจะโรแมนติก  ฟิลธรรมชาติ  ต้นไม้กางปีกอย่างร่มรื่นสุด ให้5ดาวเลยค่ะ ห้อ</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>IRH</t>
+          <t>RWK</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Imperial River House Resort</t>
+          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Chiang Rai</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>163</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
@@ -583,70 +579,78 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>IMK</t>
+          <t>IRH</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Imperial Hotel Convention Center Korat</t>
+          <t>Imperial River House Resort</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Chiang Rai</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>บริการดีมาก ห้องพักสะอาด อาหารอร่อย แนะนำที่นี่ค่ะ ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ห้องพัก สงบ สะอาด ความปลอดภัย ดีมากค่ะ ความสามารถเดินได้</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>IMC</t>
+          <t>IMK</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Imperial Chiang Mai Resort and Sport Club</t>
+          <t>Imperial Hotel Convention Center Korat</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Chiang Mai</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>ห้องพักค่อนข้างเก่า…แอร์ไม่เย็นเท่าที่ควร…เร่งพัดลมสุดแล้ว ลมแทบไม่ออกเลย…เปิดทิ้งไว้ตอน 2 ทุ่ม กลับห้องมาตี 2 ห้องยังไม่เย็นเท่าไหร่เลย… ห้องน้ำ เปิดน้ำมาตอนแรก น้ำแดงเป็นสนิม สงสัยจะไม่มีคนเข้าพักมา</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>RWC</t>
+          <t>IMC</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Raweekanlaya Wellness Cuisine Resort</t>
+          <t>Imperial Chiang Mai Resort and Sport Club</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -660,12 +664,16 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>ร่มรื่นมากเงียบสงบ สระว่ายน้ำกว้างใหญ่ สภาพสระว่ายน้ำดีมากไม่มีกระเบื้องแตกเลย สระมีความสกปรกเล็กน้อยมีใบไม้และเศษอะไรเล็กๆอยู่ตรงผิวน้ำทั่วสระ สระเด็กค่อนข้างไม่สะอาดเลย ประเภทการเดินทาง วันหยุดพักผ่</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -689,12 +697,16 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>ดีครบด้าน ห้องพักกว้าง สะอาด แอร์เย็น อาหารดี มีให้เลือกหลากหลาย อร่อยทุกอย่าง ห้องประชุมดี พนักงานบริการดีมาก ๆ ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 อาหา</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -776,12 +788,16 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>ตั้งใจที่จะมาพักที่นี่สักครั้งนึงเพราะเห็นว่าโลเคชั่นดี อยู่ในลิสต์โรงแรมนึงในเชียงใหม่ที่จะมาเลยแหละ แต่พอมาถึงแล้วแอบผิดหวัง และไม่น่ากลับมาอีก  รายละเอียดการจองลูกค้า 1 คน ตอนมาเช็กอินก็ 1 คน แต่ได</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -863,32 +879,40 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>ที่ตั้งอยู่ใจกลางเมืองทำเลดีไปไหนก็สะดวกและที่สำคัญไม่วุ่นวายครับ</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>IBC</t>
+          <t>RWC</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
+          <t>Raweekanlaya Wellness Cuisine Resort</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Petchaburi</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr"/>
+          <t>Chiang Mai</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="n">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
@@ -906,7 +930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -919,7 +943,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>รอบนี้ (2026-07-13 04:32) มีรีวิวใหม่ 5 รายการ | เทียบรอบก่อน 2026-07-06 14:17</t>
+          <t>รอบนี้ (2026-07-20 04:36) มีรีวิวใหม่ 11 รายการ | เทียบรอบก่อน 2026-07-13 04:32</t>
         </is>
       </c>
     </row>
@@ -953,115 +977,253 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>RWK</t>
+          <t>IRH</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
+          <t>Imperial River House Resort</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>pattamarat thongmar</t>
+          <t>สุมาลี สุอำ</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>ประทับใจในการบริการของเจ้าหน้าที่ทุกท่าน  มืออาชีพ  ห้องพักนอนสบาย    พนักงานทุกคนยิ้มแย้มแจ่มใส ชอบมากที่สุด กับบรรยากาศที่สุดแสนจะโรแมนติก  ฟิลธรรมชาติ  ต้นไม้กางปีกอย่างร่มรื่นสุด ให้5ดาวเลยค่ะ ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+          <t>บริการดีมาก ห้องพักสะอาด อาหารอร่อย แนะนำที่นี่ค่ะ ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ห้องพัก สงบ สะอาด ความปลอดภัย ดีมากค่ะ ความสามารถเดินได้ เดินเล่นได้ปลอดภัย อาหารและเครื่องดื่ม อาหารอร่อย รายละเอียดที่น่าสนใจ มีสระว่ายน้ำสะอาด ฟิสเนส น่าเล่นมากๆค่ะ ไฮไลต์ของโรงแรม หรูหรา วิวสวย โรแมนติก เงียบสงบ เหมาะสำหรับเด็ก คุ้มค่า และ ไฮเทค</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>RWK</t>
+          <t>IMC</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
+          <t>Imperial Chiang Mai Resort and Sport Club</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Sakontorn Udomsalee</t>
+          <t>Garfield</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>เป็นสถานที่ hidden gem ใน Bangkok เลยก็ว่าได้ หากใครต้องการหลีกความวุ่นวาย มาพักผ่อน ฮีลใจ ที่นี่ก็เป็นทางเลือกหนึ่ง บรรยากาศสงบ และที่สำคัญคืออาหารอร่อย ได้รสชาติไทยจริงๆ ได้ทาน isan set มีแกงอ่อม ลาบ ส้มตำ ไก่ทอด น้ำพริกปลาร้า ไส้กรอกอีสาน ทานจนหมดเลย ชอบน้ำพริกปลาร้ามากๆ ทานมาหลายที่แล้ว แต่ที่นี่ทำอร่อยกว่าที่อื่นมาก  ที่นี่มี สปา นวดไทย และนวดน้ำมัน ด้วย เนื่องจากจุดประสงค์ครั้งนี้คือ ผ่อนคลายความเครียด เลยเลือกนวดน้ำมัน หมอนวดคือ คุณหมอมีนา และปรียา ช่วยแนะนำและนวดให้ กล้ามเนื้อที่ตึงๆจากการทำงาน เลยเบาขึ้น แถมยังผ่อนคลายความเหนื่อยล้าได้ดีอีกด้วย ถือว่ารักษากายใจ ก่อนเริ่มงานต่อไป ได้เลิศๆ ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว คู่รัก ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม เงียบสงบ</t>
+          <t>ร่มรื่นมากเงียบสงบ สระว่ายน้ำกว้างใหญ่ สภาพสระว่ายน้ำดีมากไม่มีกระเบื้องแตกเลย สระมีความสกปรกเล็กน้อยมีใบไม้และเศษอะไรเล็กๆอยู่ตรงผิวน้ำทั่วสระ สระเด็กค่อนข้างไม่สะอาดเลย ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว คู่รัก ไฮไลต์ของโรงแรม เงียบสงบ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>RWK</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
+          <t>Imm Hotel Thapae</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>LiNGEX</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>เป็นโรงแรมทีมีมีสวนที่สวยและน่าทึ่ง อะเมซอนในกรุงเทพ บรรยากาศเงียบสงบ เหมาะแก่การพักผ่อน อาหารไทยรสชาติดี พนักงานน่ารักทุกคน โดยเฉพาะน้องๆรีเซฟชั่น ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+          <t>ตั้งใจที่จะมาพักที่นี่สักครั้งนึงเพราะเห็นว่าโลเคชั่นดี อยู่ในลิสต์โรงแรมนึงในเชียงใหม่ที่จะมาเลยแหละ แต่พอมาถึงแล้วแอบผิดหวัง และไม่น่ากลับมาอีก  รายละเอียดการจองลูกค้า 1 คน ตอนมาเช็กอินก็ 1 คน แต่ได้เตียงที่มีรอยต่อ เหมือนสองเตียงแบบนี้ ไม่เข้าใจเหมือนกันค่ะ  โถงกินอาหารเช้าอยู่กลางโรงแรมเลย ในขณะที่ชั้น 1 ก็มีห้องของลูกค้าเยอะแยะอยู่มากมายตรงนั้น เสียงช้อนกระทบจานตั้งแต่เช้าตรู่ บางกลุ่มมากินข้าวแล้วเกิดอรรถรสพูดคุยเสียงดังอีก  จากที่จะมาพักผ่อนเสียอารมณ์มาก ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว เดินทางลำพัง ห้องพัก: 3 บริการ: 3 สถานที่ตั้ง: 5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>RWK</t>
+          <t>IPL</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Ratchanee Ritthidej</t>
+          <t>Bongz Zuperbong</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>พนักงานบริการใส่ใจดีมาก ห้องพักสวยมี detail และเอกลักษณ์มาก บรรยากาศร่มรื่น อาหารเช้าเป็นบุฟเฟต์อร่อย สะอาด ต้นไม้เยอะมากค่ะ ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+          <t>ดีครบด้าน ห้องพักกว้าง สะอาด แอร์เย็น อาหารดี มีให้เลือกหลากหลาย อร่อยทุกอย่าง ห้องประชุมดี พนักงานบริการดีมาก ๆ ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 อาหารและเครื่องดื่ม อาหารอร่อยมาก พนักงานบริการดี คอยเติมของตลอด ยิ้มแย้มแจ่มใส กาแฟก็อร่อย ราคาไม่แพง ไฮไลต์ของโรงแรม เงียบสงบ และ คุ้มค่า</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>RWK</t>
+          <t>IPL</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>สาธิดา อุ้มญาติ</t>
+          <t>Sugimoto Okamura</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>บรรยากาศดีมากเลยค่ะ อาหารอร่อยมากเลยค่ะปกติไม่ทานอาหารโบราณนะคะแต่มาทานที่นี่อาหารอร่อยมากเลยค่ะ ติดใจเลย ได้ลองใช้บริการสปาดู พนักงานนวดสปาก็ดีมากเลยค่ะ ทุกอย่างดูสะอาด ภาพรวมโอเคมากเลยค่ะ กลับมาอีกแน่นอน เต็มสิบไม่หักก 💯 ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม วิวสวย เงียบสงบ และ คุ้มค่า</t>
+          <t>ประทับใจทุกอย่างค่ะ พนักงาน ห้องพัก รายอาหาร แต่กลางคืนแอร์ไม่ค่อยเย็นนิดนึง มาเย็นเกือบเช้าๆ แต่ก็ไม่เป็นไรค่ะ ยังพอรับได้ ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว คู่รัก ห้องพัก: 4 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม หรูหรา เงียบสงบ และ คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>IPL</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Thi Wanan</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>พนักงานบริการดีมาก ห้องพักสะอาด  สระว่ายน้ำสะอาด คุณลุงกุ๊กในห้องอาหารตอนเช้าใจดีมาก อาหารอร่อย ไว้คราวหน้ามาพิษณุโลกจะมาพักอีกค่ะ ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม หรูหรา วิวสวย โรแมนติก เงียบสงบ เหมาะสำหรับเด็ก และ คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>IPL</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>วีรภัทร อุดมศักดิ์พิบูลย์</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>ปลั๊กไฟใช้ไม่ได้บางจุด แอร์ไม่ค่อยเย็น ส่วนยิมและอาหารเช้าดีเลย ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>IPL</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Tny JeemD.</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>พนักงานบริการดีมากค่ะ ห้องพักสะอาด สระว่ายน้ำใหญ่มาก อาหารอร่อย ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว เดินทางลำพัง ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม หรูหรา วิวสวย เงียบสงบ และ คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>IMK</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Korat</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>TUBE TK</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>ห้องพักค่อนข้างเก่า…แอร์ไม่เย็นเท่าที่ควร…เร่งพัดลมสุดแล้ว ลมแทบไม่ออกเลย…เปิดทิ้งไว้ตอน 2 ทุ่ม กลับห้องมาตี 2 ห้องยังไม่เย็นเท่าไหร่เลย… ห้องน้ำ เปิดน้ำมาตอนแรก น้ำแดงเป็นสนิม สงสัยจะไม่มีคนเข้าพักมานานพอสมควร…สายชำระชำรุด มีน้ำหยด ตอนแรกไม่เห็น ตื่นมาเข้าห้องน้ำ น้ำนองพื้นเพราะสายชำระชำรุด พื้นห้องน้ำไม่มีรูระบายน้ำ ต้องเอาผ้าเช็ดเท้าซับน้ำ บิดน้ำทิ้งลงอ่างอาบน้ำอยู่พักนึง… ตอนเช็คเอ้าท์ โทรเรียกให้พนักงานมาช่วยขนกระเป๋า รออยู่เกิน 15 นาที…เลยตัดสินใจขนลงไปเองดีกว่า รอนานเกินไป ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว คู่รัก ห้องพัก: 2 บริการ: 3 สถานที่ตั้ง: 4 ไฮไลต์ของโรงแรม เงียบสงบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>IMK</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Korat</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Jee S</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>ไปรอเช็คอินน์ที่เค้าเตอร์ มือนึงอุ้มเด็กหลับก็หยิบบัตรประชาชนยืนรอคิวปกติ เห็นอีกฝั่งว่างก็ยืนรอตรงนั้นเผื่อมีพนักงานอีกคนมาบริการ ถ้าไม่มีก็รอคิวต่อพี่ผู้หญิงที่มาก่อน ยังไม่ทันอ้าปากพูดอะไร พนักงานบอก "พี่ไปนั่งก่อนนะครับผมให้บริการท่านนี้อยู่ พอดีพี่เค้ามาก่อน "😐 เราคิดในใจอ้าวยังไม่ได้พูดอะไรเลยแค่ยืนรอ ทำไมพูดเหมือนเราจะแซงคิว ก็เลยตอบกลับไปว่า ด้วยน้ำเสียงแข็งไปเลย "พี่ยังไม่ได้ว่าอะไรเลย พี่ก็แค่ยืนรอ ก็รู้อยู่ว่าพี่ผู้หญิงเค้ามาก่อน ก็รอให้ตัวเองให้บริการเค้าเสร็จ พี่ถึงจะพูด ก็รู้จักความอยู่ " เอาตรงๆไม่พอใจค่ะ ทำไมมีคำพูดเยอะแยะในการพูดกับลูกค้าทำไมเลือกพูดแบบนั้นมา ควรอบรมพนักงานบ้างนะคะ ยิ้มบ้างก็ดีค่ะ ไม่ใช่ต่อว่าลูกค้าเลย เรายังไม่พูดอะไรสักคำ ว่าจะไม่นอนล่ะแต่มันดึกก็เลยนอน -ส่วนพนักงานขนของดูแลดี -ที่จอดรถต้องลงไปจอดด้านล่าง -สระว่ายน้ำ บริการอื่นๆคงดีมั้ง -ห้องน้ำไม่สะอาด มีผมคนอื่น มีขนคนอื่นอยู่  คงไม่มาอีกล่ะคะ ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 2 บริการ: 2 สถานที่ตั้ง: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Narathiwat Hotel</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Mr. Thanathach “COKE Adventure” Tuntiyaskun</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>ที่ตั้งอยู่ใจกลางเมืองทำเลดีไปไหนก็สะดวกและที่สำคัญไม่วุ่นวายครับ</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2744,6 +2906,126 @@
         <v>5</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>IMC</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Imperial Chiang Mai Resort and Sport Club</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>IMK</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Korat</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Imperial Narathiwat Hotel</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>IPL</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>IRH</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Imperial River House Resort</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Imm Hotel Thapae</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/report.xlsx
+++ b/report.xlsx
@@ -540,12 +540,16 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>โรงแรมไม่ใหญ่มากแต่น่ารัก มีบ้านหลังพลูวิลล่าติดทะเลสำหรับครอบครัวที่มีเด็กและคนแก่ 😁 สระว่ายน้ำส่วนตัว และส่วนกลาง ดีมาก ชายหาดทะเลอยู่หน้าบ้านเลย ฟินสุด คือไม่ต้องเดินไกล มีอาหารเช้าบุฟเฟ่ นอนหลับสบ</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -601,136 +605,124 @@
         <v>164</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>บริการดีมาก ห้องพักสะอาด อาหารอร่อย แนะนำที่นี่ค่ะ ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ห้องพัก สงบ สะอาด ความปลอดภัย ดีมากค่ะ ความสามารถเดินได้</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>IMK</t>
+          <t>RWC</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Imperial Hotel Convention Center Korat</t>
+          <t>Raweekanlaya Wellness Cuisine Resort</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Chiang Mai</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>ห้องพักค่อนข้างเก่า…แอร์ไม่เย็นเท่าที่ควร…เร่งพัดลมสุดแล้ว ลมแทบไม่ออกเลย…เปิดทิ้งไว้ตอน 2 ทุ่ม กลับห้องมาตี 2 ห้องยังไม่เย็นเท่าไหร่เลย… ห้องน้ำ เปิดน้ำมาตอนแรก น้ำแดงเป็นสนิม สงสัยจะไม่มีคนเข้าพักมา</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>IMC</t>
+          <t>IMK</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Imperial Chiang Mai Resort and Sport Club</t>
+          <t>Imperial Hotel Convention Center Korat</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Chiang Mai</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>ร่มรื่นมากเงียบสงบ สระว่ายน้ำกว้างใหญ่ สภาพสระว่ายน้ำดีมากไม่มีกระเบื้องแตกเลย สระมีความสกปรกเล็กน้อยมีใบไม้และเศษอะไรเล็กๆอยู่ตรงผิวน้ำทั่วสระ สระเด็กค่อนข้างไม่สะอาดเลย ประเภทการเดินทาง วันหยุดพักผ่</t>
+          <t xml:space="preserve">The Imperial Hotel &amp; Convention Centre Korat - ศูนย์ประชุมและที่พักระดับมาตรฐานสากลใจกลางโคราช ประทับใจมากค่ะ! ที่นี่สมกับเป็นหนึ่งในศูนย์ประชุมและโรงแรมชั้นนำของเมืองโคราช ตัวศูนย์ประชุม (Convention </t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>IPL</t>
+          <t>IMC</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Imperial Hotel Convention Center Phitsanulok</t>
+          <t>Imperial Chiang Mai Resort and Sport Club</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Phitsanulok</t>
+          <t>Chiang Mai</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>ดีครบด้าน ห้องพักกว้าง สะอาด แอร์เย็น อาหารดี มีให้เลือกหลากหลาย อร่อยทุกอย่าง ห้องประชุมดี พนักงานบริการดีมาก ๆ ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 อาหา</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TSB</t>
+          <t>IPL</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>The Tantawan Hotel Surawong Bangkok</t>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Phitsanulok</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
@@ -740,12 +732,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>PLB</t>
+          <t>TSB</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
+          <t>The Tantawan Hotel Surawong Bangkok</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -759,7 +751,7 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
@@ -769,17 +761,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>PLB</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Imm Hotel Thapae</t>
+          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Chiang Mai</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -788,26 +780,22 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>ตั้งใจที่จะมาพักที่นี่สักครั้งนึงเพราะเห็นว่าโลเคชั่นดี อยู่ในลิสต์โรงแรมนึงในเชียงใหม่ที่จะมาเลยแหละ แต่พอมาถึงแล้วแอบผิดหวัง และไม่น่ากลับมาอีก  รายละเอียดการจองลูกค้า 1 คน ตอนมาเช็กอินก็ 1 คน แต่ได</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>IUV</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Imperial Urban Villas Chiang Mai</t>
+          <t>Imm Hotel Thapae</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -821,7 +809,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
@@ -831,12 +819,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>CHH</t>
+          <t>IUV</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CH Hotel Chiang Mai</t>
+          <t>Imperial Urban Villas Chiang Mai</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -846,11 +834,11 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
@@ -860,17 +848,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>CHH</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Imperial Narathiwat Hotel</t>
+          <t>CH Hotel Chiang Mai</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Narathiwat</t>
+          <t>Chiang Mai</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -879,40 +867,36 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>ที่ตั้งอยู่ใจกลางเมืองทำเลดีไปไหนก็สะดวกและที่สำคัญไม่วุ่นวายครับ</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>RWC</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Raweekanlaya Wellness Cuisine Resort</t>
+          <t>Imperial Narathiwat Hotel</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Chiang Mai</t>
+          <t>Narathiwat</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
@@ -930,7 +914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -943,7 +927,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>รอบนี้ (2026-07-20 04:36) มีรีวิวใหม่ 11 รายการ | เทียบรอบก่อน 2026-07-13 04:32</t>
+          <t>รอบนี้ (2026-07-27 04:37) มีรีวิวใหม่ 2 รายการ | เทียบรอบก่อน 2026-07-20 04:36</t>
         </is>
       </c>
     </row>
@@ -977,253 +961,46 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>IRH</t>
+          <t>IMK</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Imperial River House Resort</t>
+          <t>Imperial Hotel Convention Center Korat</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>สุมาลี สุอำ</t>
+          <t>kanokon phuethongsa</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>บริการดีมาก ห้องพักสะอาด อาหารอร่อย แนะนำที่นี่ค่ะ ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ห้องพัก สงบ สะอาด ความปลอดภัย ดีมากค่ะ ความสามารถเดินได้ เดินเล่นได้ปลอดภัย อาหารและเครื่องดื่ม อาหารอร่อย รายละเอียดที่น่าสนใจ มีสระว่ายน้ำสะอาด ฟิสเนส น่าเล่นมากๆค่ะ ไฮไลต์ของโรงแรม หรูหรา วิวสวย โรแมนติก เงียบสงบ เหมาะสำหรับเด็ก คุ้มค่า และ ไฮเทค</t>
+          <t>The Imperial Hotel &amp; Convention Centre Korat - ศูนย์ประชุมและที่พักระดับมาตรฐานสากลใจกลางโคราช ประทับใจมากค่ะ! ที่นี่สมกับเป็นหนึ่งในศูนย์ประชุมและโรงแรมชั้นนำของเมืองโคราช ตัวศูนย์ประชุม (Convention Centre) และห้องแกรนด์บอลรูมใหญ่โต โอ่โถง อุปกรณ์แสงสีเสียงครบครัน ทันสมัย เหมาะกับการจัดงานสัมมนา งานแต่งงาน หรืออีเวนต์ใหญ่ ๆ มากค่ะ ในส่วนของห้องพัก กว้างขวาง สะอาด เตียงนอนนุ่มสบาย สิ่งอำนวยความสะดวกครบครัน สระว่ายน้ำใหญ่และฟิตเนสดีมาก อาหารเช้าและอาหารจัดเลี้ยงรสชาติอร่อยได้มาตรฐาน พนักงานทุกแผนกมีความเป็นมืออาชีพ บริการรวดเร็ว และที่จอดรถกว้างขวางรองรับรถได้จำนวนมาก สะดวกสบายครบวงจรจริง ๆ แนะนำเลยค่ะ! 🏢✨ ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม หรูหรา วิวสวย โรแมนติก เงียบสงบ คุ้มค่า และ ไฮเทค</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>IMC</t>
+          <t>IBC</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Imperial Chiang Mai Resort and Sport Club</t>
+          <t>Imperial Beachfront Resort Cha-am</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Garfield</t>
+          <t>Utaranee Chanasongkarm</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>ร่มรื่นมากเงียบสงบ สระว่ายน้ำกว้างใหญ่ สภาพสระว่ายน้ำดีมากไม่มีกระเบื้องแตกเลย สระมีความสกปรกเล็กน้อยมีใบไม้และเศษอะไรเล็กๆอยู่ตรงผิวน้ำทั่วสระ สระเด็กค่อนข้างไม่สะอาดเลย ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว คู่รัก ไฮไลต์ของโรงแรม เงียบสงบ</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>ITC</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Imm Hotel Thapae</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>ตั้งใจที่จะมาพักที่นี่สักครั้งนึงเพราะเห็นว่าโลเคชั่นดี อยู่ในลิสต์โรงแรมนึงในเชียงใหม่ที่จะมาเลยแหละ แต่พอมาถึงแล้วแอบผิดหวัง และไม่น่ากลับมาอีก  รายละเอียดการจองลูกค้า 1 คน ตอนมาเช็กอินก็ 1 คน แต่ได้เตียงที่มีรอยต่อ เหมือนสองเตียงแบบนี้ ไม่เข้าใจเหมือนกันค่ะ  โถงกินอาหารเช้าอยู่กลางโรงแรมเลย ในขณะที่ชั้น 1 ก็มีห้องของลูกค้าเยอะแยะอยู่มากมายตรงนั้น เสียงช้อนกระทบจานตั้งแต่เช้าตรู่ บางกลุ่มมากินข้าวแล้วเกิดอรรถรสพูดคุยเสียงดังอีก  จากที่จะมาพักผ่อนเสียอารมณ์มาก ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว เดินทางลำพัง ห้องพัก: 3 บริการ: 3 สถานที่ตั้ง: 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>IPL</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Hotel Convention Center Phitsanulok</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Bongz Zuperbong</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>ดีครบด้าน ห้องพักกว้าง สะอาด แอร์เย็น อาหารดี มีให้เลือกหลากหลาย อร่อยทุกอย่าง ห้องประชุมดี พนักงานบริการดีมาก ๆ ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 อาหารและเครื่องดื่ม อาหารอร่อยมาก พนักงานบริการดี คอยเติมของตลอด ยิ้มแย้มแจ่มใส กาแฟก็อร่อย ราคาไม่แพง ไฮไลต์ของโรงแรม เงียบสงบ และ คุ้มค่า</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>IPL</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Hotel Convention Center Phitsanulok</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Sugimoto Okamura</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>ประทับใจทุกอย่างค่ะ พนักงาน ห้องพัก รายอาหาร แต่กลางคืนแอร์ไม่ค่อยเย็นนิดนึง มาเย็นเกือบเช้าๆ แต่ก็ไม่เป็นไรค่ะ ยังพอรับได้ ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว คู่รัก ห้องพัก: 4 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม หรูหรา เงียบสงบ และ คุ้มค่า</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>IPL</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Hotel Convention Center Phitsanulok</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Thi Wanan</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>พนักงานบริการดีมาก ห้องพักสะอาด  สระว่ายน้ำสะอาด คุณลุงกุ๊กในห้องอาหารตอนเช้าใจดีมาก อาหารอร่อย ไว้คราวหน้ามาพิษณุโลกจะมาพักอีกค่ะ ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม หรูหรา วิวสวย โรแมนติก เงียบสงบ เหมาะสำหรับเด็ก และ คุ้มค่า</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>IPL</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Hotel Convention Center Phitsanulok</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>วีรภัทร อุดมศักดิ์พิบูลย์</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr"/>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>ปลั๊กไฟใช้ไม่ได้บางจุด แอร์ไม่ค่อยเย็น ส่วนยิมและอาหารเช้าดีเลย ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>IPL</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Hotel Convention Center Phitsanulok</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Tny JeemD.</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr"/>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>พนักงานบริการดีมากค่ะ ห้องพักสะอาด สระว่ายน้ำใหญ่มาก อาหารอร่อย ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว เดินทางลำพัง ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม หรูหรา วิวสวย เงียบสงบ และ คุ้มค่า</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>IMK</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Hotel Convention Center Korat</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>TUBE TK</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr"/>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>ห้องพักค่อนข้างเก่า…แอร์ไม่เย็นเท่าที่ควร…เร่งพัดลมสุดแล้ว ลมแทบไม่ออกเลย…เปิดทิ้งไว้ตอน 2 ทุ่ม กลับห้องมาตี 2 ห้องยังไม่เย็นเท่าไหร่เลย… ห้องน้ำ เปิดน้ำมาตอนแรก น้ำแดงเป็นสนิม สงสัยจะไม่มีคนเข้าพักมานานพอสมควร…สายชำระชำรุด มีน้ำหยด ตอนแรกไม่เห็น ตื่นมาเข้าห้องน้ำ น้ำนองพื้นเพราะสายชำระชำรุด พื้นห้องน้ำไม่มีรูระบายน้ำ ต้องเอาผ้าเช็ดเท้าซับน้ำ บิดน้ำทิ้งลงอ่างอาบน้ำอยู่พักนึง… ตอนเช็คเอ้าท์ โทรเรียกให้พนักงานมาช่วยขนกระเป๋า รออยู่เกิน 15 นาที…เลยตัดสินใจขนลงไปเองดีกว่า รอนานเกินไป ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว คู่รัก ห้องพัก: 2 บริการ: 3 สถานที่ตั้ง: 4 ไฮไลต์ของโรงแรม เงียบสงบ</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>IMK</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Hotel Convention Center Korat</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Jee S</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr"/>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>ไปรอเช็คอินน์ที่เค้าเตอร์ มือนึงอุ้มเด็กหลับก็หยิบบัตรประชาชนยืนรอคิวปกติ เห็นอีกฝั่งว่างก็ยืนรอตรงนั้นเผื่อมีพนักงานอีกคนมาบริการ ถ้าไม่มีก็รอคิวต่อพี่ผู้หญิงที่มาก่อน ยังไม่ทันอ้าปากพูดอะไร พนักงานบอก "พี่ไปนั่งก่อนนะครับผมให้บริการท่านนี้อยู่ พอดีพี่เค้ามาก่อน "😐 เราคิดในใจอ้าวยังไม่ได้พูดอะไรเลยแค่ยืนรอ ทำไมพูดเหมือนเราจะแซงคิว ก็เลยตอบกลับไปว่า ด้วยน้ำเสียงแข็งไปเลย "พี่ยังไม่ได้ว่าอะไรเลย พี่ก็แค่ยืนรอ ก็รู้อยู่ว่าพี่ผู้หญิงเค้ามาก่อน ก็รอให้ตัวเองให้บริการเค้าเสร็จ พี่ถึงจะพูด ก็รู้จักความอยู่ " เอาตรงๆไม่พอใจค่ะ ทำไมมีคำพูดเยอะแยะในการพูดกับลูกค้าทำไมเลือกพูดแบบนั้นมา ควรอบรมพนักงานบ้างนะคะ ยิ้มบ้างก็ดีค่ะ ไม่ใช่ต่อว่าลูกค้าเลย เรายังไม่พูดอะไรสักคำ ว่าจะไม่นอนล่ะแต่มันดึกก็เลยนอน -ส่วนพนักงานขนของดูแลดี -ที่จอดรถต้องลงไปจอดด้านล่าง -สระว่ายน้ำ บริการอื่นๆคงดีมั้ง -ห้องน้ำไม่สะอาด มีผมคนอื่น มีขนคนอื่นอยู่  คงไม่มาอีกล่ะคะ ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 2 บริการ: 2 สถานที่ตั้ง: 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Narathiwat Hotel</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Mr. Thanathach “COKE Adventure” Tuntiyaskun</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr"/>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>ที่ตั้งอยู่ใจกลางเมืองทำเลดีไปไหนก็สะดวกและที่สำคัญไม่วุ่นวายครับ</t>
+          <t>โรงแรมไม่ใหญ่มากแต่น่ารัก มีบ้านหลังพลูวิลล่าติดทะเลสำหรับครอบครัวที่มีเด็กและคนแก่ 😁 สระว่ายน้ำส่วนตัว และส่วนกลาง ดีมาก ชายหาดทะเลอยู่หน้าบ้านเลย ฟินสุด คือไม่ต้องเดินไกล มีอาหารเช้าบุฟเฟ่ นอนหลับสบาย ตื่นมาเปิดประตูห้องนอน เจอสระว่ายน้ำ+ได้ยินเสียงคลื่นเจอทะเล พร้อมกระโดดลงน้ำมาก แถมโรงแรมน่ารักมาก ให้เช็คอินออกบ่ายโมงได้ เพราะคนมารับติดธุระ ไว้หายตัวดำ จะกลับไปตำอีกแน่นอน 🩵🩵 ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
         </is>
       </c>
     </row>
@@ -2235,7 +2012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3026,6 +2803,46 @@
         <v>1</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>IBC</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Imperial Beachfront Resort Cha-am</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>IMK</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Korat</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/report.xlsx
+++ b/report.xlsx
@@ -540,14 +540,14 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>โรงแรมไม่ใหญ่มากแต่น่ารัก มีบ้านหลังพลูวิลล่าติดทะเลสำหรับครอบครัวที่มีเด็กและคนแก่ 😁 สระว่ายน้ำส่วนตัว และส่วนกลาง ดีมาก ชายหาดทะเลอยู่หน้าบ้านเลย ฟินสุด คือไม่ต้องเดินไกล มีอาหารเช้าบุฟเฟ่ นอนหลับสบ</t>
+          <t>ห้อง Beachfront pool villa แอร์เย็น สมาร์ททีวี โซฟา ห้องนั่งเล่น 2 ห้องนอน 2 ห้องน้ำ มี 2 ชั้น มีสระว่ายน้ำขนาดพอประมาณ ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
         </is>
       </c>
     </row>
@@ -612,26 +612,26 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>RWC</t>
+          <t>IMK</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Raweekanlaya Wellness Cuisine Resort</t>
+          <t>Imperial Hotel Convention Center Korat</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Chiang Mai</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
@@ -641,59 +641,55 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>IMK</t>
+          <t>IMC</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Imperial Hotel Convention Center Korat</t>
+          <t>Imperial Chiang Mai Resort and Sport Club</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Chiang Mai</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The Imperial Hotel &amp; Convention Centre Korat - ศูนย์ประชุมและที่พักระดับมาตรฐานสากลใจกลางโคราช ประทับใจมากค่ะ! ที่นี่สมกับเป็นหนึ่งในศูนย์ประชุมและโรงแรมชั้นนำของเมืองโคราช ตัวศูนย์ประชุม (Convention </t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>IMC</t>
+          <t>IPL</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Imperial Chiang Mai Resort and Sport Club</t>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Chiang Mai</t>
+          <t>Phitsanulok</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -703,26 +699,26 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>IPL</t>
+          <t>TSB</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Imperial Hotel Convention Center Phitsanulok</t>
+          <t>The Tantawan Hotel Surawong Bangkok</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Phitsanulok</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
@@ -732,12 +728,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>TSB</t>
+          <t>PLB</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>The Tantawan Hotel Surawong Bangkok</t>
+          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -751,7 +747,7 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
@@ -761,17 +757,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>PLB</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
+          <t>Imm Hotel Thapae</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Chiang Mai</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -780,7 +776,7 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
@@ -790,12 +786,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>IUV</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Imm Hotel Thapae</t>
+          <t>Imperial Urban Villas Chiang Mai</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -809,22 +805,26 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>จองห้องไว้เป็นเดือนๆ ขอเตียงเดี่ยว 2 เตียงคู่ 2 พอมาเช็คอินได้เตียงเดี่ยวแค่ห้องเดียว คุยกับพนง.ขอเตียงเดี่ยวชั้นไหนก็ได้ก็ไม่ยอมหาให้ แถมยังพูดว่าให้ใครคนใดคนนึงไปนอนโซฟา แล้วปิดประตูกั้นเอา พูดแบบนี</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>IUV</t>
+          <t>CHH</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Imperial Urban Villas Chiang Mai</t>
+          <t>CH Hotel Chiang Mai</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -834,11 +834,11 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
@@ -848,17 +848,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>CHH</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>CH Hotel Chiang Mai</t>
+          <t>Imperial Narathiwat Hotel</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Chiang Mai</t>
+          <t>Narathiwat</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -867,36 +867,36 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>ห้องพักเก่าไปหน่อย แต่สะอาดและได้รับการปรับปรุงบ้างแล้ว ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 4 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม เงียบสงบ และ คุ้มค่า</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>RWC</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Imperial Narathiwat Hotel</t>
+          <t>Raweekanlaya Wellness Cuisine Resort</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Narathiwat</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
-      </c>
+          <t>Chiang Mai</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
@@ -914,7 +914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>รอบนี้ (2026-07-27 04:37) มีรีวิวใหม่ 2 รายการ | เทียบรอบก่อน 2026-07-20 04:36</t>
+          <t>รอบนี้ (2026-08-03 04:31) มีรีวิวใหม่ 3 รายการ | เทียบรอบก่อน 2026-07-27 04:37</t>
         </is>
       </c>
     </row>
@@ -961,46 +961,69 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>IMK</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Imperial Hotel Convention Center Korat</t>
+          <t>Imperial Narathiwat Hotel</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>kanokon phuethongsa</t>
+          <t>PEAR</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>The Imperial Hotel &amp; Convention Centre Korat - ศูนย์ประชุมและที่พักระดับมาตรฐานสากลใจกลางโคราช ประทับใจมากค่ะ! ที่นี่สมกับเป็นหนึ่งในศูนย์ประชุมและโรงแรมชั้นนำของเมืองโคราช ตัวศูนย์ประชุม (Convention Centre) และห้องแกรนด์บอลรูมใหญ่โต โอ่โถง อุปกรณ์แสงสีเสียงครบครัน ทันสมัย เหมาะกับการจัดงานสัมมนา งานแต่งงาน หรืออีเวนต์ใหญ่ ๆ มากค่ะ ในส่วนของห้องพัก กว้างขวาง สะอาด เตียงนอนนุ่มสบาย สิ่งอำนวยความสะดวกครบครัน สระว่ายน้ำใหญ่และฟิตเนสดีมาก อาหารเช้าและอาหารจัดเลี้ยงรสชาติอร่อยได้มาตรฐาน พนักงานทุกแผนกมีความเป็นมืออาชีพ บริการรวดเร็ว และที่จอดรถกว้างขวางรองรับรถได้จำนวนมาก สะดวกสบายครบวงจรจริง ๆ แนะนำเลยค่ะ! 🏢✨ ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม หรูหรา วิวสวย โรแมนติก เงียบสงบ คุ้มค่า และ ไฮเทค</t>
+          <t>ห้องพักเก่าไปหน่อย แต่สะอาดและได้รับการปรับปรุงบ้างแล้ว ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 4 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม เงียบสงบ และ คุ้มค่า</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>IBC</t>
+          <t>IUV</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
+          <t>Imperial Urban Villas Chiang Mai</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Utaranee Chanasongkarm</t>
+          <t>Trraann</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>โรงแรมไม่ใหญ่มากแต่น่ารัก มีบ้านหลังพลูวิลล่าติดทะเลสำหรับครอบครัวที่มีเด็กและคนแก่ 😁 สระว่ายน้ำส่วนตัว และส่วนกลาง ดีมาก ชายหาดทะเลอยู่หน้าบ้านเลย ฟินสุด คือไม่ต้องเดินไกล มีอาหารเช้าบุฟเฟ่ นอนหลับสบาย ตื่นมาเปิดประตูห้องนอน เจอสระว่ายน้ำ+ได้ยินเสียงคลื่นเจอทะเล พร้อมกระโดดลงน้ำมาก แถมโรงแรมน่ารักมาก ให้เช็คอินออกบ่ายโมงได้ เพราะคนมารับติดธุระ ไว้หายตัวดำ จะกลับไปตำอีกแน่นอน 🩵🩵 ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+          <t>จองห้องไว้เป็นเดือนๆ ขอเตียงเดี่ยว 2 เตียงคู่ 2 พอมาเช็คอินได้เตียงเดี่ยวแค่ห้องเดียว คุยกับพนง.ขอเตียงเดี่ยวชั้นไหนก็ได้ก็ไม่ยอมหาให้ แถมยังพูดว่าให้ใครคนใดคนนึงไปนอนโซฟา แล้วปิดประตูกั้นเอา พูดแบบนี้ออกมาได้ยังไง ราคาห้องตั้ง 1500 บาท การบริการและการดูแลลูกค้าติดลบขั้นสุด ไม่มีความคุ้มค่าราคา และการบริการที่ดีเลย ตัวโรงแรมก็เก่ามาก ห้องน้ำก็มีเชื้อราเต็มไปหมด ไม่แนะนำที่นี่ค่ะ เราว่ามีโรงแรมอื่นที่พร้อมให้บริการที่ดีกว่าที่นี่เยอะมากค่ะ ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 1 บริการ: 1 สถานที่ตั้ง: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>IBC</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Beachfront Resort Cha-am</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>NOPPAKAO Masuwan</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>ห้อง Beachfront pool villa แอร์เย็น สมาร์ททีวี โซฟา ห้องนั่งเล่น 2 ห้องนอน 2 ห้องน้ำ มี 2 ชั้น มีสระว่ายน้ำขนาดพอประมาณ ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2843,6 +2866,66 @@
         <v>1</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>IBC</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Imperial Beachfront Resort Cha-am</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>Imperial Narathiwat Hotel</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>IUV</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>Imperial Urban Villas Chiang Mai</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/report.xlsx
+++ b/report.xlsx
@@ -521,50 +521,46 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>IBC</t>
+          <t>RWC</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
+          <t>Raweekanlaya Wellness Cuisine Resort</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Petchaburi</t>
+          <t>Chiang Mai</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>22</v>
+        <v>160</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>ห้อง Beachfront pool villa แอร์เย็น สมาร์ททีวี โซฟา ห้องนั่งเล่น 2 ห้องนอน 2 ห้องน้ำ มี 2 ชั้น มีสระว่ายน้ำขนาดพอประมาณ ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>RWK</t>
+          <t>IBC</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
+          <t>Imperial Beachfront Resort Cha-am</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Petchaburi</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -573,36 +569,40 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>ประทับใจ เซอร์วิสมาย และการดูแล ของเจ้าหน้าที่ที่นี่มากครับ ขอบคุณนะครับที่ทำให้ ขอบคุณนะครับที่ทำให้ทริปของเราดีขึ้นแม้จะมีปัญหาบ้าง  แนะนำจองห้อง Duplex ครับ ประทับใจมาก อาหารเช้าถือว่าปกติ ไม่แย่แล</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>IRH</t>
+          <t>RWK</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Imperial River House Resort</t>
+          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Chiang Rai</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>164</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
@@ -612,26 +612,26 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>IMK</t>
+          <t>IRH</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Imperial Hotel Convention Center Korat</t>
+          <t>Imperial River House Resort</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Chiang Rai</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
@@ -641,55 +641,59 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>IMC</t>
+          <t>IMK</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Imperial Chiang Mai Resort and Sport Club</t>
+          <t>Imperial Hotel Convention Center Korat</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Chiang Mai</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>อาหารที่โรงแรมอร่อยมาก เรามา2ครั้งแล้ว ประทับใจกับการที่ปรับเปลี่ยนลิฟต์ให้ลิงค์กับห้องพัก เพื่อความปลอดภัยของลูกค้า ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 5 บริการ: 5 สถานที่</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>IPL</t>
+          <t>IMC</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Imperial Hotel Convention Center Phitsanulok</t>
+          <t>Imperial Chiang Mai Resort and Sport Club</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Phitsanulok</t>
+          <t>Chiang Mai</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>0</v>
@@ -699,41 +703,45 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TSB</t>
+          <t>IPL</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>The Tantawan Hotel Surawong Bangkok</t>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Phitsanulok</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>โรงแรมใหญ่มากก นอนสบายสุดๆแบบเตียงดูด แต่ห้องน้ำอาจจะเก่าไปหน่อย น้ำแรง แต่ฝักบัวคือต้องเกษียณอายุได้แล้วค่าาาา~ อาหารเช้าเริ่ดๆ ก๋วยเตี๋ยวอร่อยมาก โดยเฉพาะลูกชิ้น ไม่เคยกินอะไรแบบนี้เลย อร่อยจริงๆค่า</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>PLB</t>
+          <t>TSB</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
+          <t>The Tantawan Hotel Surawong Bangkok</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -747,7 +755,7 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>0</v>
@@ -757,17 +765,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>PLB</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Imm Hotel Thapae</t>
+          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Chiang Mai</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -776,22 +784,26 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>ห้องสกปรกตามรูป ฝุ่นเยอะะมากๆ ไฟในห้องมืดเกินไป ลานจอดรถเหม็นอับ ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 1 บริการ: 2 สถานที่ตั้ง: 2</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>IUV</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Imperial Urban Villas Chiang Mai</t>
+          <t>Imm Hotel Thapae</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -805,26 +817,26 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>จองห้องไว้เป็นเดือนๆ ขอเตียงเดี่ยว 2 เตียงคู่ 2 พอมาเช็คอินได้เตียงเดี่ยวแค่ห้องเดียว คุยกับพนง.ขอเตียงเดี่ยวชั้นไหนก็ได้ก็ไม่ยอมหาให้ แถมยังพูดว่าให้ใครคนใดคนนึงไปนอนโซฟา แล้วปิดประตูกั้นเอา พูดแบบนี</t>
+          <t>สำหรับเราถือว่าอยู่ในเกณฑ์ดี พอได้ ถ้ามาเที่ยวแบบไม่ได้ต้องการพักผ่อน  ‼️ ที่นี่ไม่เหมาะกับคนที่ต้องการพักผ่อน แบบเงียบสงบ ‼️หรือคนที่มีปัญหาการนอนหลับ เนื่องจาก อาคารออกแบบมา แบบไม่ได้เก็บเสียง ตั้งแ</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>CHH</t>
+          <t>IUV</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CH Hotel Chiang Mai</t>
+          <t>Imperial Urban Villas Chiang Mai</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -834,11 +846,11 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
@@ -848,17 +860,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>CHH</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Imperial Narathiwat Hotel</t>
+          <t>CH Hotel Chiang Mai</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Narathiwat</t>
+          <t>Chiang Mai</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -867,36 +879,40 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>ห้องพักเก่าไปหน่อย แต่สะอาดและได้รับการปรับปรุงบ้างแล้ว ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 4 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม เงียบสงบ และ คุ้มค่า</t>
+          <t>ที่จอดรถก็มี น้ำไหลแรง แอร์เย็น อาหารเช้าก็โอเค เอาไรมาไม่เริศ โรงแรมรีโนเวทแล้วระบบก็ยังดีอยู่ ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>RWC</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Raweekanlaya Wellness Cuisine Resort</t>
+          <t>Imperial Narathiwat Hotel</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Chiang Mai</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr"/>
+          <t>Narathiwat</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="n">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
@@ -914,7 +930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -927,7 +943,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>รอบนี้ (2026-08-03 04:31) มีรีวิวใหม่ 3 รายการ | เทียบรอบก่อน 2026-07-27 04:37</t>
+          <t>รอบนี้ (2026-08-10 03:11) มีรีวิวใหม่ 11 รายการ | เทียบรอบก่อน 2026-08-03 04:31</t>
         </is>
       </c>
     </row>
@@ -961,69 +977,253 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>PLB</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Imperial Narathiwat Hotel</t>
+          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>PEAR</t>
+          <t>tidaporn nakin</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>ห้องพักเก่าไปหน่อย แต่สะอาดและได้รับการปรับปรุงบ้างแล้ว ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 4 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม เงียบสงบ และ คุ้มค่า</t>
+          <t>ห้องสกปรกตามรูป ฝุ่นเยอะะมากๆ ไฟในห้องมืดเกินไป ลานจอดรถเหม็นอับ ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 1 บริการ: 2 สถานที่ตั้ง: 2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>IUV</t>
+          <t>PLB</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Imperial Urban Villas Chiang Mai</t>
+          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Trraann</t>
+          <t>Panukon Kaohom</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>จองห้องไว้เป็นเดือนๆ ขอเตียงเดี่ยว 2 เตียงคู่ 2 พอมาเช็คอินได้เตียงเดี่ยวแค่ห้องเดียว คุยกับพนง.ขอเตียงเดี่ยวชั้นไหนก็ได้ก็ไม่ยอมหาให้ แถมยังพูดว่าให้ใครคนใดคนนึงไปนอนโซฟา แล้วปิดประตูกั้นเอา พูดแบบนี้ออกมาได้ยังไง ราคาห้องตั้ง 1500 บาท การบริการและการดูแลลูกค้าติดลบขั้นสุด ไม่มีความคุ้มค่าราคา และการบริการที่ดีเลย ตัวโรงแรมก็เก่ามาก ห้องน้ำก็มีเชื้อราเต็มไปหมด ไม่แนะนำที่นี่ค่ะ เราว่ามีโรงแรมอื่นที่พร้อมให้บริการที่ดีกว่าที่นี่เยอะมากค่ะ ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 1 บริการ: 1 สถานที่ตั้ง: 1</t>
+          <t>เก่า - อับ - สกปรก - ยามไม่ดี - ที่จอดใต้ดินดีแต่กลิ่นเหม็น โดยรวมแล้ว หนีไป หนีไป หนีไป ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 1 บริการ: 1 สถานที่ตั้ง: 4 ห้องพัก เก่า - อับ - สกปรก ความปลอดภัย ไม่ค่อย อาหารและเครื่องดื่ม อาหารเช้าไม่ดี - เมื่อเทียบกับราคา ที่อื่นดีกว่า รายละเอียดที่น่าสนใจ หนีไป</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>IBC</t>
+          <t>CHH</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
+          <t>CH Hotel Chiang Mai</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>NOPPAKAO Masuwan</t>
+          <t>รุ่งนภา โยทะพันธ์</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>ห้อง Beachfront pool villa แอร์เย็น สมาร์ททีวี โซฟา ห้องนั่งเล่น 2 ห้องนอน 2 ห้องน้ำ มี 2 ชั้น มีสระว่ายน้ำขนาดพอประมาณ ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+          <t>ที่จอดรถก็มี น้ำไหลแรง แอร์เย็น อาหารเช้าก็โอเค เอาไรมาไม่เริศ โรงแรมรีโนเวทแล้วระบบก็ยังดีอยู่ ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Imm Hotel Thapae</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Missis Thiphy</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>สำหรับเราถือว่าอยู่ในเกณฑ์ดี พอได้ ถ้ามาเที่ยวแบบไม่ได้ต้องการพักผ่อน  ‼️ ที่นี่ไม่เหมาะกับคนที่ต้องการพักผ่อน แบบเงียบสงบ ‼️หรือคนที่มีปัญหาการนอนหลับ เนื่องจาก อาคารออกแบบมา แบบไม่ได้เก็บเสียง ตั้งแต่ชั้น1 ไปถึงชั้น3 ดังทะลุถึงกันหมด รวมถึงเสียงลากกนะเป๋า เสียงคนเดินคุยระหว่างทางเดินก็เช่นกัน  🥐🍽️ เสียงคนทานข้าวมื้อเช้า เสียงจานช้อน ดังไปถึงชั้น3  📍 แต่โลเคชั่นดีมากอยู่ใจกลางเมือง สามารถเดินเที่ยววัด หรือแวะร้านอาหารคาเฟ่ต่างๆได้สะดวก  ✅ ชอบมากตรงที่ด้านหน้าโรงแรม ออกมาก็มีร้านพันธุ์ไทย 🥤 และแมคโดนัลด์ 🍗 ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว คู่รัก ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>IPL</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>ɹɹnnɓɹɐʍ</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>โรงแรมใหญ่มากก นอนสบายสุดๆแบบเตียงดูด แต่ห้องน้ำอาจจะเก่าไปหน่อย น้ำแรง แต่ฝักบัวคือต้องเกษียณอายุได้แล้วค่าาาา~ อาหารเช้าเริ่ดๆ ก๋วยเตี๋ยวอร่อยมาก โดยเฉพาะลูกชิ้น ไม่เคยกินอะไรแบบนี้เลย อร่อยจริงๆค่า อยากให้มาลองกัน มาพักอีกแน่นอนรอบหน้า ห้องพัก: 4 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>IPL</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Maepoo Namping</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>พวกเราเกินทางมาจากเชียงใหม่มาพักที่นี่2คืนประทับใจมากทั้งการบริการห้องพักพนักงานสวัสดีต้อนรับทักทายทุกคนตั้งแต่เชคอินจนถึงเชคเอ้าท์....พนักงานในห้องอาหารบริการดีทุกคนยิ้มแย้มแจ่มใสเชฟตรงเคาน์เตอร์น่ารักลูกสาวเดินไปขอนมข้นทั้ง2วันก็เดินมาให้ที่โต๊ะพร้อมกับบอกว่าทางให้อร่อยนะครับ♥️นิ้มแย้มแจ่มใส กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ห้องพัก สะอาด กิจกรรมในบริเวณใกล้เคียง สระว่ายน้ำสะอาด ความปลอดภัย บริการด้านความปลอดภัย อาหารและเครื่องดื่ม อร่อยสะอาด ไฮไลต์ของโรงแรม คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>IMK</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Korat</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>The_shadow</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>อาหารที่โรงแรมอร่อยมาก เรามา2ครั้งแล้ว ประทับใจกับการที่ปรับเปลี่ยนลิฟต์ให้ลิงค์กับห้องพัก เพื่อความปลอดภัยของลูกค้า ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม หรูหรา วิวสวย และ คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>IBC</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Beachfront Resort Cha-am</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Ikekkx</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>ประทับใจ เซอร์วิสมาย และการดูแล ของเจ้าหน้าที่ที่นี่มากครับ ขอบคุณนะครับที่ทำให้ ขอบคุณนะครับที่ทำให้ทริปของเราดีขึ้นแม้จะมีปัญหาบ้าง  แนะนำจองห้อง Duplex ครับ ประทับใจมาก อาหารเช้าถือว่าปกติ ไม่แย่และไม่ได้ว้าวครับ  ทำเลที่นี่ Beachfront จริงๆครับ สระว่ายน้ำโรงแรมไม่ใหญ่มาก  มาช่วงเทศกาลคนเยอะหน่อยครับ ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว คู่รัก ห้องพัก: 3 บริการ: 5 สถานที่ตั้ง: 4 ไฮไลต์ของโรงแรม หรูหรา วิวสวย โรแมนติก และ คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>IBC</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Beachfront Resort Cha-am</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>กินไป กับเจา</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>ห้องไม่เก็บเสียง อาหารเช้าธรรมดาค่ะ (แอบมีข้ามต้มไก่)ภาพรวมก็เหมาะกับเด็กครอบครัวเล็กๆค่ะ  เล่นทรายหน้าโรงแรมได้ ไปมา เสาร์18.7.69 ห้องพัก: 3 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>IBC</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Beachfront Resort Cha-am</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>กินวันละร้าน กับ อ.ใบหม่อน</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>(Translated by Google) Eco Cozy Beachfront is a beautiful hotel with a great atmosphere, located on Ban Bangket Beach, just before Cha-am Beach. I loved the view from the swimming pool; it's stunning and you can enjoy the sea view from there.  The hotel isn't huge, but it has a private beach that's very peaceful. Watching the sunrise in the morning is truly beautiful.  They offer various room types including Pool Villas, Pool Access, Sea View, and Garden View rooms, all with a varied breakfast menu.  I chose a Garden View room. The view wasn't anything spectacular, but the room was spacious. Overall, it was great.  (Original) Eco Cozy Beachfront is a beautiful hotel with a great atmosphere, located on Ban Bangket Beach, just before Cha-am Beach. I loved the view from the swimming pool; it's stunning and you can enjoy the sea view from there.  The hotel isn't huge, but it has a private beach that's very peaceful. Watching the sunrise in the morning is truly beautiful.  They offer various room types, including Pool Villas, Pool Access, Sea View, and Garden View rooms, all with a varied breakfast menu.  I chose a Garden View room. The view wasn't anything spectacular, but the room was spacious. Overall, it was great. Woke up early to watch the sunrise, it was truly beautiful.  The rooms include Pool Villa, Pool Access, Sea View, and Garden View, with a varied breakfast included.  I chose a Garden View room. The view wasn't anything spectacular, but the room was spacious. Overall, it was okay.  (Original) (Translated by Google) Eco Cozy Beachfront is a beautiful hotel with a great atmosphere, located on Ban Bangket Beach, just before Cha-am Beach. I loved the view from the swimming pool; it's stunning and you can enjoy the sea view from there.  The hotel isn't huge, but it has a private beach that's very peaceful. Watching the sunrise in the morning is truly beautiful.  They offer various room types including Pool Villas, Pool Access, Sea View, and Garden View rooms, all with a varied breakfast menu.  I chose a Garden View room. The view wasn't anything spectacular, but the room was spacious. Overall, it was great.  (Original) Eco Cozy Beachfront โรงแรมสวย บรรยากาศดี พิกัด หาดบ้านบางเกตุ ก่อนถึงหาดชะอำแป๊บนึง ชอบวิวตรงสระว่ายน้ำมาก สวย ชมทะเลได้ด้วย . โรงแรมไม่ถึงกับใหญ่มาก เค้ามีหาดส่วนตัว หาดตรงนี้สงบด้วย ตื่นเช้ามาดูพระอาทิตย์ขึ้น สวยจริงๆ . ห้องพัก เค้ามีทั้ง Pool Villa, Pool Access, Sea View, Garden View รวมอาหารเช้าหลากหลายอยู่ . เลือกพักห้อง Garden View วิวไม่มีอะไร แต่ห้องกว้างอยู่นะ รวมๆ ก็โอเคเลย ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 4 ไฮไลต์ของโรงแรม วิวสวย</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>IBC</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Beachfront Resort Cha-am</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>นงลักษณ์ เด็ดแก้ว</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>ที่พักสะอาดห้องสวยดีพนักบริการดีวิวสวยมากเดินลงชมวิวทะเลได้เลยใก้ลๆสระว่ายร้ำในห้องก็สะอาดน้ำใสเย็นสะบายดีมากมาพักกันได้เลยค่ะชอบมาก ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ไฮไลต์ของโรงแรม หรูหรา วิวสวย เงียบสงบ และ คุ้มค่า</t>
         </is>
       </c>
     </row>
@@ -1179,16 +1379,16 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>รัชดา สุขใจ</t>
+          <t>Panukon Kaohom</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>ห้องไม่เก็บเสียงเลย ได้ยินสารพูดเสียง เสียงลากเก้าอี้ดังตลอดเวลา รวมถึงแม่บ้านทำความสะอาดก็เสียงดังเช่นเดียวกัน เคยพักมาหลายที่แต่ที่นี่คือเป็นการพักผ่อนที่ไม่ดีเลย ควรปรับปรุงหรือมีกฎเรื่องเสียงดังจะดีมาก</t>
+          <t>เก่า - อับ - สกปรก - ยามไม่ดี - ที่จอดใต้ดินดีแต่กลิ่นเหม็น โดยรวมแล้ว หนีไป หนีไป หนีไป ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 1 บริการ: 1 สถานที่ตั้ง: 4 ห้องพัก เก่า - อับ - สกปรก ความปลอดภัย ไม่ค่อย อาหารและเครื่องดื่ม อาหารเช้าไม่ดี - เมื่อเทียบกับราคา ที่อื่นดีกว่า รายละเอียดที่น่าสนใจ หนีไป</t>
         </is>
       </c>
     </row>
@@ -1205,16 +1405,16 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>DNA- TH</t>
+          <t>รัชดา สุขใจ</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2024-04-27 เข้าพักครั้งแรก ก่อนไปก็คิดว่าจะเดินเล่นห้างเดอะมอล์ล บางกะปิ แต่พอไปถึงก็เหนื่อย.  ไปพักผ่อนจริงๆ เดินต่อป้ายรถเมล์ไกลไปนิดเพราะรถเมล์ไม่ได้ผ่านโดยตรง .  มาถึงก็แวะนวดก่อน ๑ ชม. ในตัวอาคารนี่แหล่ะ ได้ชั่วโมงละ๑๐๐บาท. ก็ดีแหล่ะนะ.  ระหว่างเข้าไปรอเช็คอิน.ก็ก่อน๑๔น. พนง.ที่ล็อบบี้ ก็ยืนคุยกันเอง เป็นกันเองมากๆ (กะเพื่อนพนักงานกันเองน่ะ) เสียงก็ดังอยู่นะ พื้นที่นั่งรอก็มินิดเดียว .  สภาพห้องก็พอดีแหล่ะ แต่พอมามุมห้องน้ำก็มีร่องรอยฝุ่นเต็มๆ แถวที่ดูดอากาศน่ะนะ มุมระเบียงเข้าใจว่ากันนก ก็เลยต้องตีตาข่าย .  ประตูห้องไม่เก็บเสียงเลย นี่เลือกจ่ายห้องที่แพงขึ้นมาเป็น Delux แล้ว ก็ดันอยู่ตรงข้ามกับห้อง Suprem ที่เสียง นทท.จีนเล็ดลอดผ่านประตูที่ไม่เก็บเสียงเลย  อาหารเช้าถือว่าปานกลาง ไม่ถึงกับว๊าวนัก . มีหลากหลายอยู่ในแบบว่า เค็มก็เค็ม จืดก็จืด.  โดยรวมๆ ถือว่าราคาสูง สำหรับราคา Booking ตรงแล้ว พันนิดๆ รวมอาหารเช้า.  วันรุ่งขึ้นรีบออกไปชมหนังก่อนเที่ยงราคา๙๙บาท อิอิ ประหยัดดี ที่โลตัส</t>
+          <t>ห้องไม่เก็บเสียงเลย ได้ยินสารพูดเสียง เสียงลากเก้าอี้ดังตลอดเวลา รวมถึงแม่บ้านทำความสะอาดก็เสียงดังเช่นเดียวกัน เคยพักมาหลายที่แต่ที่นี่คือเป็นการพักผ่อนที่ไม่ดีเลย ควรปรับปรุงหรือมีกฎเรื่องเสียงดังจะดีมาก</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1431,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Julie Xie</t>
+          <t>DNA- TH</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr"/>
@@ -1240,7 +1440,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>โรงแรมตั้งอยู่ติดกับตลาดสดที่มีกลิ่นเหม็น ห้องพักมีกลิ่นเหมือนถุงเท้าเหม็น อากาศไม่ดี และผ้าปูที่นอนทำให้ฉันคันตลอดทั้งคืนจนถึงตี 3 ทำให้ฉันนอนไม่หลับ เครื่องปรับอากาศเสียงดังมากเหมือนเครื่องปั่นไฟ ทำให้พักผ่อนไม่ได้เลย  โรงแรมนี้เป็นการผสมผสานระหว่างตลาดสดและห้างสรรพสินค้าขนาดเล็ก ทางเข้าและทางออกจะถูกล็อคในเวลากลางคืน หากไม่มีเจ้าหน้าที่รักษาความปลอดภัย คุณจะไม่สามารถเข้าหรือออกได้ คุณต้องเปิดประตูเล็กๆ ผ่านร้านสะดวกซื้อเพื่อออกไป  ไม่มีอะไรอยู่ใกล้ๆ ร้านอาหารและบาร์อยู่ไกล ทำให้ไม่สะดวก  หลังจากได้รับกุญแจแล้ว เรานั่งรถบัสไปกินข้าวและซื้อของ หลังจากอาบน้ำและเตรียมตัวเข้านอน ตั้งแต่ 22.00 น. ถึง 3.00 น. ฉันรู้สึกไม่สบายตัวมากจนนอนไม่หลับ เราติดต่อแผนกต้อนรับ แต่ไม่มีการตอบกลับใดๆ เลย เราจองไว้สามคืน และเราหนีออกจากสถานที่แย่ๆ นี้ในคืนแรก—เราทนอยู่ต่อไม่ได้แม้แต่สักนาทีเดียว!  คำเตือน: ⚠️⚠️⚠️ ภาพถ่ายเหล่านี้ถ่ายไว้เมื่อหลายปีก่อนและอยู่ในสภาพไม่ดี</t>
+          <t>2024-04-27 เข้าพักครั้งแรก ก่อนไปก็คิดว่าจะเดินเล่นห้างเดอะมอล์ล บางกะปิ แต่พอไปถึงก็เหนื่อย.  ไปพักผ่อนจริงๆ เดินต่อป้ายรถเมล์ไกลไปนิดเพราะรถเมล์ไม่ได้ผ่านโดยตรง .  มาถึงก็แวะนวดก่อน ๑ ชม. ในตัวอาคารนี่แหล่ะ ได้ชั่วโมงละ๑๐๐บาท. ก็ดีแหล่ะนะ.  ระหว่างเข้าไปรอเช็คอิน.ก็ก่อน๑๔น. พนง.ที่ล็อบบี้ ก็ยืนคุยกันเอง เป็นกันเองมากๆ (กะเพื่อนพนักงานกันเองน่ะ) เสียงก็ดังอยู่นะ พื้นที่นั่งรอก็มินิดเดียว .  สภาพห้องก็พอดีแหล่ะ แต่พอมามุมห้องน้ำก็มีร่องรอยฝุ่นเต็มๆ แถวที่ดูดอากาศน่ะนะ มุมระเบียงเข้าใจว่ากันนก ก็เลยต้องตีตาข่าย .  ประตูห้องไม่เก็บเสียงเลย นี่เลือกจ่ายห้องที่แพงขึ้นมาเป็น Delux แล้ว ก็ดันอยู่ตรงข้ามกับห้อง Suprem ที่เสียง นทท.จีนเล็ดลอดผ่านประตูที่ไม่เก็บเสียงเลย  อาหารเช้าถือว่าปานกลาง ไม่ถึงกับว๊าวนัก . มีหลากหลายอยู่ในแบบว่า เค็มก็เค็ม จืดก็จืด.  โดยรวมๆ ถือว่าราคาสูง สำหรับราคา Booking ตรงแล้ว พันนิดๆ รวมอาหารเช้า.  วันรุ่งขึ้นรีบออกไปชมหนังก่อนเที่ยงราคา๙๙บาท อิอิ ประหยัดดี ที่โลตัส</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2926,6 +3126,126 @@
         <v>1</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>CHH</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>CH Hotel Chiang Mai</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>IBC</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Imperial Beachfront Resort Cha-am</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>IMK</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Korat</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>IPL</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>Imm Hotel Thapae</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>PLB</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/report.xlsx
+++ b/report.xlsx
@@ -521,46 +521,50 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>RWC</t>
+          <t>IBC</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Raweekanlaya Wellness Cuisine Resort</t>
+          <t>Imperial Beachfront Resort Cha-am</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Chiang Mai</t>
+          <t>Petchaburi</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>160</v>
+        <v>30</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>เพิ่งเคยมาครั้งแรก เรามาถึง 14.30 น. แต่ห้องยังไม่เรียบร้อย เลยนั่งรอที่ล็อบบี้ เดินไปดูหาดที่ห้องอาหาร พนักงานทุกจุดบริการดีมากเลยค่ะ ห้องพักสะดวกสบายมากค่ะ มีที่จอดรถ เสียดายที่ฝนตก เราเพิ่งเดินหาดไ</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>IBC</t>
+          <t>RWK</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
+          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Petchaburi</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -569,40 +573,36 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>ประทับใจ เซอร์วิสมาย และการดูแล ของเจ้าหน้าที่ที่นี่มากครับ ขอบคุณนะครับที่ทำให้ ขอบคุณนะครับที่ทำให้ทริปของเราดีขึ้นแม้จะมีปัญหาบ้าง  แนะนำจองห้อง Duplex ครับ ประทับใจมาก อาหารเช้าถือว่าปกติ ไม่แย่แล</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>RWK</t>
+          <t>IRH</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
+          <t>Imperial River House Resort</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Chiang Rai</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5</v>
+        <v>164</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
@@ -612,17 +612,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>IRH</t>
+          <t>RWC</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Imperial River House Resort</t>
+          <t>Raweekanlaya Wellness Cuisine Resort</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Chiang Rai</t>
+          <t>Chiang Mai</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
@@ -663,13 +663,9 @@
         <v>172</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>อาหารที่โรงแรมอร่อยมาก เรามา2ครั้งแล้ว ประทับใจกับการที่ปรับเปลี่ยนลิฟต์ให้ลิงค์กับห้องพัก เพื่อความปลอดภัยของลูกค้า ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 5 บริการ: 5 สถานที่</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -689,7 +685,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
@@ -725,13 +721,9 @@
         <v>176</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>โรงแรมใหญ่มากก นอนสบายสุดๆแบบเตียงดูด แต่ห้องน้ำอาจจะเก่าไปหน่อย น้ำแรง แต่ฝักบัวคือต้องเกษียณอายุได้แล้วค่าาาา~ อาหารเช้าเริ่ดๆ ก๋วยเตี๋ยวอร่อยมาก โดยเฉพาะลูกชิ้น ไม่เคยกินอะไรแบบนี้เลย อร่อยจริงๆค่า</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -784,14 +776,14 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>ห้องสกปรกตามรูป ฝุ่นเยอะะมากๆ ไฟในห้องมืดเกินไป ลานจอดรถเหม็นอับ ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 1 บริการ: 2 สถานที่ตั้ง: 2</t>
+          <t>ห้องน่ารัก reception หอม พนักงานต้อนรับดี ยิ้มแย้มดี ทางเดินกว้าง สะอาด โลเคชั่นดีมาก เดินออกมาเจอตลาดเลยของกินเยอะมาก แต่เจอแมลงสาปตายในห้องน้ำ ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว เพื่อน ห้องพัก:</t>
         </is>
       </c>
     </row>
@@ -817,14 +809,14 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>สำหรับเราถือว่าอยู่ในเกณฑ์ดี พอได้ ถ้ามาเที่ยวแบบไม่ได้ต้องการพักผ่อน  ‼️ ที่นี่ไม่เหมาะกับคนที่ต้องการพักผ่อน แบบเงียบสงบ ‼️หรือคนที่มีปัญหาการนอนหลับ เนื่องจาก อาคารออกแบบมา แบบไม่ได้เก็บเสียง ตั้งแ</t>
+          <t>โรงแรมอยู่ตรงข้ามประตูท่าแพ มีที่จอดรถด้านหลัง ใกล้แหล่งของกิน ด้านหน้าเป็นร้านแม๊คโดนัล ก้องพักสะอาด ห้องน้ำสะอาด แอร์เย็น เตียงนอนสบาย อาหารเช้ามีข้าสวย กะหล่ำปรีผัดน้ำปลา กะกล่ำดอกผัด ข้าวผัด ไข่ดา</t>
         </is>
       </c>
     </row>
@@ -882,13 +874,9 @@
         <v>161</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>ที่จอดรถก็มี น้ำไหลแรง แอร์เย็น อาหารเช้าก็โอเค เอาไรมาไม่เริศ โรงแรมรีโนเวทแล้วระบบก็ยังดีอยู่ ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -930,7 +918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -943,7 +931,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>รอบนี้ (2026-08-10 03:11) มีรีวิวใหม่ 11 รายการ | เทียบรอบก่อน 2026-08-03 04:31</t>
+          <t>รอบนี้ (2026-08-17 02:19) มีรีวิวใหม่ 6 รายการ | เทียบรอบก่อน 2026-08-10 03:11</t>
         </is>
       </c>
     </row>
@@ -987,243 +975,128 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>tidaporn nakin</t>
+          <t>Natty K</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>ห้องสกปรกตามรูป ฝุ่นเยอะะมากๆ ไฟในห้องมืดเกินไป ลานจอดรถเหม็นอับ ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 1 บริการ: 2 สถานที่ตั้ง: 2</t>
+          <t>ห้องน่ารัก reception หอม พนักงานต้อนรับดี ยิ้มแย้มดี ทางเดินกว้าง สะอาด โลเคชั่นดีมาก เดินออกมาเจอตลาดเลยของกินเยอะมาก แต่เจอแมลงสาปตายในห้องน้ำ ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 4 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม เงียบสงบ</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>PLB</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
+          <t>Imm Hotel Thapae</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Panukon Kaohom</t>
+          <t>SOMJEED 268</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>เก่า - อับ - สกปรก - ยามไม่ดี - ที่จอดใต้ดินดีแต่กลิ่นเหม็น โดยรวมแล้ว หนีไป หนีไป หนีไป ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 1 บริการ: 1 สถานที่ตั้ง: 4 ห้องพัก เก่า - อับ - สกปรก ความปลอดภัย ไม่ค่อย อาหารและเครื่องดื่ม อาหารเช้าไม่ดี - เมื่อเทียบกับราคา ที่อื่นดีกว่า รายละเอียดที่น่าสนใจ หนีไป</t>
+          <t>โรงแรมอยู่ตรงข้ามประตูท่าแพ มีที่จอดรถด้านหลัง ใกล้แหล่งของกิน ด้านหน้าเป็นร้านแม๊คโดนัล ก้องพักสะอาด ห้องน้ำสะอาด แอร์เย็น เตียงนอนสบาย อาหารเช้ามีข้าสวย กะหล่ำปรีผัดน้ำปลา กะกล่ำดอกผัด ข้าวผัด ไข่ดาว ไส้กรอกไก่ ไส้กรอกหมู จองผ่านแอปอโกด้ามา คุ้มค่าค่ะ พนักงานบริการดีมากค่ะ ห้องพัก: 4 บริการ: 5 สถานที่ตั้ง: 5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>CHH</t>
+          <t>IBC</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>CH Hotel Chiang Mai</t>
+          <t>Imperial Beachfront Resort Cha-am</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>รุ่งนภา โยทะพันธ์</t>
+          <t>เอ็ก สุรางคนา</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>ที่จอดรถก็มี น้ำไหลแรง แอร์เย็น อาหารเช้าก็โอเค เอาไรมาไม่เริศ โรงแรมรีโนเวทแล้วระบบก็ยังดีอยู่ ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+          <t>เพิ่งเคยมาครั้งแรก เรามาถึง 14.30 น. แต่ห้องยังไม่เรียบร้อย เลยนั่งรอที่ล็อบบี้ เดินไปดูหาดที่ห้องอาหาร พนักงานทุกจุดบริการดีมากเลยค่ะ ห้องพักสะดวกสบายมากค่ะ มีที่จอดรถ เสียดายที่ฝนตก เราเพิ่งเดินหาดได้แพพเดียว ไว้จะมาพักอีกแน่นอนค่ะ ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ห้องพัก สะอาด เงียบ กิจกรรมในบริเวณใกล้เคียง ร้านอาหารยินดี อร่อยค่ะ ความปลอดภัย ปลอดภัยดีค่ะ ความสามารถเดินได้ หน้าหาดเดินได้ค่ะ อาหารและเครื่องดื่ม เราจองมาเป็นราคาที่รวมอาหารเช้าค่ะ รายละเอียดที่น่าสนใจ บรรยากาศดีค่ะ ไฮไลต์ของโรงแรม เงียบสงบ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>IBC</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Imm Hotel Thapae</t>
+          <t>Imperial Beachfront Resort Cha-am</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Missis Thiphy</t>
+          <t>sasina samranjit</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>สำหรับเราถือว่าอยู่ในเกณฑ์ดี พอได้ ถ้ามาเที่ยวแบบไม่ได้ต้องการพักผ่อน  ‼️ ที่นี่ไม่เหมาะกับคนที่ต้องการพักผ่อน แบบเงียบสงบ ‼️หรือคนที่มีปัญหาการนอนหลับ เนื่องจาก อาคารออกแบบมา แบบไม่ได้เก็บเสียง ตั้งแต่ชั้น1 ไปถึงชั้น3 ดังทะลุถึงกันหมด รวมถึงเสียงลากกนะเป๋า เสียงคนเดินคุยระหว่างทางเดินก็เช่นกัน  🥐🍽️ เสียงคนทานข้าวมื้อเช้า เสียงจานช้อน ดังไปถึงชั้น3  📍 แต่โลเคชั่นดีมากอยู่ใจกลางเมือง สามารถเดินเที่ยววัด หรือแวะร้านอาหารคาเฟ่ต่างๆได้สะดวก  ✅ ชอบมากตรงที่ด้านหน้าโรงแรม ออกมาก็มีร้านพันธุ์ไทย 🥤 และแมคโดนัลด์ 🍗 ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว คู่รัก ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 5</t>
+          <t>ที่พักสวย ติดทะเล วิวดี อาหารเช้ามีให้เลือกหลากหลาย ภายในห้องพักสวยสะอาด แต่อยากให้ทางโรงแรมทำความสะอาดทางเดินบนอาคาร โดนรวมถือว่าโอเค ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>IPL</t>
+          <t>IBC</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Imperial Hotel Convention Center Phitsanulok</t>
+          <t>Imperial Beachfront Resort Cha-am</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>ɹɹnnɓɹɐʍ</t>
+          <t>chadaporn sooksai</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>โรงแรมใหญ่มากก นอนสบายสุดๆแบบเตียงดูด แต่ห้องน้ำอาจจะเก่าไปหน่อย น้ำแรง แต่ฝักบัวคือต้องเกษียณอายุได้แล้วค่าาาา~ อาหารเช้าเริ่ดๆ ก๋วยเตี๋ยวอร่อยมาก โดยเฉพาะลูกชิ้น ไม่เคยกินอะไรแบบนี้เลย อร่อยจริงๆค่า อยากให้มาลองกัน มาพักอีกแน่นอนรอบหน้า ห้องพัก: 4 บริการ: 5 สถานที่ตั้ง: 5</t>
+          <t>โรงแรมบรรยากาศดีมากติดทะเล มีสระน้ำผู้ใหญ่และเด็กด้วย อาหารเช้าอร่อยห้องอาหารวิวทะเลบรรยากาศดี พนักงานบริการดีมาก</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>IPL</t>
+          <t>IBC</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Imperial Hotel Convention Center Phitsanulok</t>
+          <t>Imperial Beachfront Resort Cha-am</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Maepoo Namping</t>
+          <t>chanattanaphon maneesurat</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>พวกเราเกินทางมาจากเชียงใหม่มาพักที่นี่2คืนประทับใจมากทั้งการบริการห้องพักพนักงานสวัสดีต้อนรับทักทายทุกคนตั้งแต่เชคอินจนถึงเชคเอ้าท์....พนักงานในห้องอาหารบริการดีทุกคนยิ้มแย้มแจ่มใสเชฟตรงเคาน์เตอร์น่ารักลูกสาวเดินไปขอนมข้นทั้ง2วันก็เดินมาให้ที่โต๊ะพร้อมกับบอกว่าทางให้อร่อยนะครับ♥️นิ้มแย้มแจ่มใส กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ห้องพัก สะอาด กิจกรรมในบริเวณใกล้เคียง สระว่ายน้ำสะอาด ความปลอดภัย บริการด้านความปลอดภัย อาหารและเครื่องดื่ม อร่อยสะอาด ไฮไลต์ของโรงแรม คุ้มค่า</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>IMK</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Hotel Convention Center Korat</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>The_shadow</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr"/>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>อาหารที่โรงแรมอร่อยมาก เรามา2ครั้งแล้ว ประทับใจกับการที่ปรับเปลี่ยนลิฟต์ให้ลิงค์กับห้องพัก เพื่อความปลอดภัยของลูกค้า ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม หรูหรา วิวสวย และ คุ้มค่า</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>IBC</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Ikekkx</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr"/>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>ประทับใจ เซอร์วิสมาย และการดูแล ของเจ้าหน้าที่ที่นี่มากครับ ขอบคุณนะครับที่ทำให้ ขอบคุณนะครับที่ทำให้ทริปของเราดีขึ้นแม้จะมีปัญหาบ้าง  แนะนำจองห้อง Duplex ครับ ประทับใจมาก อาหารเช้าถือว่าปกติ ไม่แย่และไม่ได้ว้าวครับ  ทำเลที่นี่ Beachfront จริงๆครับ สระว่ายน้ำโรงแรมไม่ใหญ่มาก  มาช่วงเทศกาลคนเยอะหน่อยครับ ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว คู่รัก ห้องพัก: 3 บริการ: 5 สถานที่ตั้ง: 4 ไฮไลต์ของโรงแรม หรูหรา วิวสวย โรแมนติก และ คุ้มค่า</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>IBC</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>กินไป กับเจา</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr"/>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>ห้องไม่เก็บเสียง อาหารเช้าธรรมดาค่ะ (แอบมีข้ามต้มไก่)ภาพรวมก็เหมาะกับเด็กครอบครัวเล็กๆค่ะ  เล่นทรายหน้าโรงแรมได้ ไปมา เสาร์18.7.69 ห้องพัก: 3 บริการ: 5 สถานที่ตั้ง: 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>IBC</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>กินวันละร้าน กับ อ.ใบหม่อน</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr"/>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>(Translated by Google) Eco Cozy Beachfront is a beautiful hotel with a great atmosphere, located on Ban Bangket Beach, just before Cha-am Beach. I loved the view from the swimming pool; it's stunning and you can enjoy the sea view from there.  The hotel isn't huge, but it has a private beach that's very peaceful. Watching the sunrise in the morning is truly beautiful.  They offer various room types including Pool Villas, Pool Access, Sea View, and Garden View rooms, all with a varied breakfast menu.  I chose a Garden View room. The view wasn't anything spectacular, but the room was spacious. Overall, it was great.  (Original) Eco Cozy Beachfront is a beautiful hotel with a great atmosphere, located on Ban Bangket Beach, just before Cha-am Beach. I loved the view from the swimming pool; it's stunning and you can enjoy the sea view from there.  The hotel isn't huge, but it has a private beach that's very peaceful. Watching the sunrise in the morning is truly beautiful.  They offer various room types, including Pool Villas, Pool Access, Sea View, and Garden View rooms, all with a varied breakfast menu.  I chose a Garden View room. The view wasn't anything spectacular, but the room was spacious. Overall, it was great. Woke up early to watch the sunrise, it was truly beautiful.  The rooms include Pool Villa, Pool Access, Sea View, and Garden View, with a varied breakfast included.  I chose a Garden View room. The view wasn't anything spectacular, but the room was spacious. Overall, it was okay.  (Original) (Translated by Google) Eco Cozy Beachfront is a beautiful hotel with a great atmosphere, located on Ban Bangket Beach, just before Cha-am Beach. I loved the view from the swimming pool; it's stunning and you can enjoy the sea view from there.  The hotel isn't huge, but it has a private beach that's very peaceful. Watching the sunrise in the morning is truly beautiful.  They offer various room types including Pool Villas, Pool Access, Sea View, and Garden View rooms, all with a varied breakfast menu.  I chose a Garden View room. The view wasn't anything spectacular, but the room was spacious. Overall, it was great.  (Original) Eco Cozy Beachfront โรงแรมสวย บรรยากาศดี พิกัด หาดบ้านบางเกตุ ก่อนถึงหาดชะอำแป๊บนึง ชอบวิวตรงสระว่ายน้ำมาก สวย ชมทะเลได้ด้วย . โรงแรมไม่ถึงกับใหญ่มาก เค้ามีหาดส่วนตัว หาดตรงนี้สงบด้วย ตื่นเช้ามาดูพระอาทิตย์ขึ้น สวยจริงๆ . ห้องพัก เค้ามีทั้ง Pool Villa, Pool Access, Sea View, Garden View รวมอาหารเช้าหลากหลายอยู่ . เลือกพักห้อง Garden View วิวไม่มีอะไร แต่ห้องกว้างอยู่นะ รวมๆ ก็โอเคเลย ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 4 ไฮไลต์ของโรงแรม วิวสวย</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>IBC</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>นงลักษณ์ เด็ดแก้ว</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr"/>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>ที่พักสะอาดห้องสวยดีพนักบริการดีวิวสวยมากเดินลงชมวิวทะเลได้เลยใก้ลๆสระว่ายร้ำในห้องก็สะอาดน้ำใสเย็นสะบายดีมากมาพักกันได้เลยค่ะชอบมาก ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ไฮไลต์ของโรงแรม หรูหรา วิวสวย เงียบสงบ และ คุ้มค่า</t>
+          <t>สถานที่ = ดีมาก เงียบสงบ ติดทะเล ไม่วุ่นวาย ห้องพัก = ดีมาก ห้องกว้าง สะอาด ของในห้อง ดูดีแข็งแรง ปลั๊กไฟเยอะ สะดวกมากมาย สะว่ายน้ำ = ดี ไม่ใหญ่มาก แต่มีของเด็ก แบ่งสัดส่วน และ เชือกเตือนน้ำลึกให้เด็ก ดีมาก ***ห้องอาหารเช้า = อันนี้ผิดหวังอย่างแรง  อาหารน้อยๆ มาก มีไข่ดาว แฮม ข้าวสวย ข้าวผัด ผัดผัก กระเพราไก่ ผัดซีอิ้วไข่ ข้าวต้มหมู สลัดผัก ขนมปังปิ้ง ผลไม้ กาแฟกา ไม่ใช่กาแฟสด  น้ำผลไม้สำเร็จรูป ถูกๆ จบ...  ผิดหวังอย่างแรง ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ไฮไลต์ของโรงแรม หรูหรา วิวสวย โรแมนติก เงียบสงบ และ เหมาะสำหรับเด็ก</t>
         </is>
       </c>
     </row>
@@ -2235,7 +2108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3246,6 +3119,66 @@
         <v>2</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>IBC</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>Imperial Beachfront Resort Cha-am</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>Imm Hotel Thapae</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>PLB</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/report.xlsx
+++ b/report.xlsx
@@ -521,50 +521,46 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>IBC</t>
+          <t>RWC</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
+          <t>Raweekanlaya Wellness Cuisine Resort</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Petchaburi</t>
+          <t>Chiang Mai</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>เพิ่งเคยมาครั้งแรก เรามาถึง 14.30 น. แต่ห้องยังไม่เรียบร้อย เลยนั่งรอที่ล็อบบี้ เดินไปดูหาดที่ห้องอาหาร พนักงานทุกจุดบริการดีมากเลยค่ะ ห้องพักสะดวกสบายมากค่ะ มีที่จอดรถ เสียดายที่ฝนตก เราเพิ่งเดินหาดไ</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>RWK</t>
+          <t>IBC</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
+          <t>Imperial Beachfront Resort Cha-am</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Petchaburi</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -573,36 +569,40 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>เพิ่งเคยมาครั้งแรก เรามาถึง 14.30 น. แต่ห้องยังไม่เรียบร้อย เลยนั่งรอที่ล็อบบี้ เดินไปดูหาดที่ห้องอาหาร พนักงานทุกจุดบริการดีมากเลยค่ะ ห้องพักสะดวกสบายมากค่ะ มีที่จอดรถ เสียดายที่ฝนตก เราเพิ่งเดินหาดไ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>IRH</t>
+          <t>RWK</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Imperial River House Resort</t>
+          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Chiang Rai</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>164</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
@@ -612,17 +612,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>RWC</t>
+          <t>IRH</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Raweekanlaya Wellness Cuisine Resort</t>
+          <t>Imperial River House Resort</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Chiang Mai</t>
+          <t>Chiang Rai</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
@@ -685,7 +685,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">

--- a/report.xlsx
+++ b/report.xlsx
@@ -521,26 +521,26 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>RWC</t>
+          <t>IBC</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Raweekanlaya Wellness Cuisine Resort</t>
+          <t>Imperial Beachfront Resort Cha-am</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Chiang Mai</t>
+          <t>Petchaburi</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>160</v>
+        <v>30</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
@@ -550,17 +550,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>IBC</t>
+          <t>RWK</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
+          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Petchaburi</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -569,40 +569,36 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>เพิ่งเคยมาครั้งแรก เรามาถึง 14.30 น. แต่ห้องยังไม่เรียบร้อย เลยนั่งรอที่ล็อบบี้ เดินไปดูหาดที่ห้องอาหาร พนักงานทุกจุดบริการดีมากเลยค่ะ ห้องพักสะดวกสบายมากค่ะ มีที่จอดรถ เสียดายที่ฝนตก เราเพิ่งเดินหาดไ</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>RWK</t>
+          <t>IRH</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
+          <t>Imperial River House Resort</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Chiang Rai</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5</v>
+        <v>164</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
@@ -612,26 +608,26 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>IRH</t>
+          <t>IMK</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Imperial River House Resort</t>
+          <t>Imperial Hotel Convention Center Korat</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Chiang Rai</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
@@ -641,17 +637,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>IMK</t>
+          <t>RWC</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Imperial Hotel Convention Center Korat</t>
+          <t>Raweekanlaya Wellness Cuisine Resort</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Chiang Mai</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -660,7 +656,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
@@ -779,13 +775,9 @@
         <v>170</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>ห้องน่ารัก reception หอม พนักงานต้อนรับดี ยิ้มแย้มดี ทางเดินกว้าง สะอาด โลเคชั่นดีมาก เดินออกมาเจอตลาดเลยของกินเยอะมาก แต่เจอแมลงสาปตายในห้องน้ำ ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว เพื่อน ห้องพัก:</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -809,14 +801,14 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>โรงแรมอยู่ตรงข้ามประตูท่าแพ มีที่จอดรถด้านหลัง ใกล้แหล่งของกิน ด้านหน้าเป็นร้านแม๊คโดนัล ก้องพักสะอาด ห้องน้ำสะอาด แอร์เย็น เตียงนอนสบาย อาหารเช้ามีข้าสวย กะหล่ำปรีผัดน้ำปลา กะกล่ำดอกผัด ข้าวผัด ไข่ดา</t>
+          <t>ดี เคยมาพักหลายปีก่อนมากๆๆๆประมาณ 14-15 ปีได้ ที่นอนนุ่มเด้งดี ทีวีจอใหญ่มีเนตฟริค ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 5</t>
         </is>
       </c>
     </row>
@@ -918,7 +910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -931,7 +923,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>รอบนี้ (2026-08-17 02:19) มีรีวิวใหม่ 6 รายการ | เทียบรอบก่อน 2026-08-10 03:11</t>
+          <t>รอบนี้ (2026-08-31 06:45) มีรีวิวใหม่ 1 รายการ | เทียบรอบก่อน 2026-08-17 02:19</t>
         </is>
       </c>
     </row>
@@ -965,138 +957,23 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>PLB</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
+          <t>Imm Hotel Thapae</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Natty K</t>
+          <t>Teab</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>ห้องน่ารัก reception หอม พนักงานต้อนรับดี ยิ้มแย้มดี ทางเดินกว้าง สะอาด โลเคชั่นดีมาก เดินออกมาเจอตลาดเลยของกินเยอะมาก แต่เจอแมลงสาปตายในห้องน้ำ ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 4 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม เงียบสงบ</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>ITC</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Imm Hotel Thapae</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>SOMJEED 268</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>โรงแรมอยู่ตรงข้ามประตูท่าแพ มีที่จอดรถด้านหลัง ใกล้แหล่งของกิน ด้านหน้าเป็นร้านแม๊คโดนัล ก้องพักสะอาด ห้องน้ำสะอาด แอร์เย็น เตียงนอนสบาย อาหารเช้ามีข้าสวย กะหล่ำปรีผัดน้ำปลา กะกล่ำดอกผัด ข้าวผัด ไข่ดาว ไส้กรอกไก่ ไส้กรอกหมู จองผ่านแอปอโกด้ามา คุ้มค่าค่ะ พนักงานบริการดีมากค่ะ ห้องพัก: 4 บริการ: 5 สถานที่ตั้ง: 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>IBC</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>เอ็ก สุรางคนา</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>เพิ่งเคยมาครั้งแรก เรามาถึง 14.30 น. แต่ห้องยังไม่เรียบร้อย เลยนั่งรอที่ล็อบบี้ เดินไปดูหาดที่ห้องอาหาร พนักงานทุกจุดบริการดีมากเลยค่ะ ห้องพักสะดวกสบายมากค่ะ มีที่จอดรถ เสียดายที่ฝนตก เราเพิ่งเดินหาดได้แพพเดียว ไว้จะมาพักอีกแน่นอนค่ะ ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ห้องพัก สะอาด เงียบ กิจกรรมในบริเวณใกล้เคียง ร้านอาหารยินดี อร่อยค่ะ ความปลอดภัย ปลอดภัยดีค่ะ ความสามารถเดินได้ หน้าหาดเดินได้ค่ะ อาหารและเครื่องดื่ม เราจองมาเป็นราคาที่รวมอาหารเช้าค่ะ รายละเอียดที่น่าสนใจ บรรยากาศดีค่ะ ไฮไลต์ของโรงแรม เงียบสงบ</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>IBC</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>sasina samranjit</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>ที่พักสวย ติดทะเล วิวดี อาหารเช้ามีให้เลือกหลากหลาย ภายในห้องพักสวยสะอาด แต่อยากให้ทางโรงแรมทำความสะอาดทางเดินบนอาคาร โดนรวมถือว่าโอเค ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>IBC</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>chadaporn sooksai</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>โรงแรมบรรยากาศดีมากติดทะเล มีสระน้ำผู้ใหญ่และเด็กด้วย อาหารเช้าอร่อยห้องอาหารวิวทะเลบรรยากาศดี พนักงานบริการดีมาก</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>IBC</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>chanattanaphon maneesurat</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>สถานที่ = ดีมาก เงียบสงบ ติดทะเล ไม่วุ่นวาย ห้องพัก = ดีมาก ห้องกว้าง สะอาด ของในห้อง ดูดีแข็งแรง ปลั๊กไฟเยอะ สะดวกมากมาย สะว่ายน้ำ = ดี ไม่ใหญ่มาก แต่มีของเด็ก แบ่งสัดส่วน และ เชือกเตือนน้ำลึกให้เด็ก ดีมาก ***ห้องอาหารเช้า = อันนี้ผิดหวังอย่างแรง  อาหารน้อยๆ มาก มีไข่ดาว แฮม ข้าวสวย ข้าวผัด ผัดผัก กระเพราไก่ ผัดซีอิ้วไข่ ข้าวต้มหมู สลัดผัก ขนมปังปิ้ง ผลไม้ กาแฟกา ไม่ใช่กาแฟสด  น้ำผลไม้สำเร็จรูป ถูกๆ จบ...  ผิดหวังอย่างแรง ประเภทการเดินทาง วันหยุดพักผ่อน กลุ่มท่องเที่ยว ครอบครัว ไฮไลต์ของโรงแรม หรูหรา วิวสวย โรแมนติก เงียบสงบ และ เหมาะสำหรับเด็ก</t>
+          <t>ดี เคยมาพักหลายปีก่อนมากๆๆๆประมาณ 14-15 ปีได้ ที่นอนนุ่มเด้งดี ทีวีจอใหญ่มีเนตฟริค ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 5</t>
         </is>
       </c>
     </row>
@@ -2108,7 +1985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3179,6 +3056,26 @@
         <v>1</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>Imm Hotel Thapae</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/report.xlsx
+++ b/report.xlsx
@@ -569,12 +569,16 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>ห้องอาหารใช้กุ้งเน่ามาทำอาหารสังเกตุจากกุ้งเก็บนานเริ่มดำ หางดำ เน่า และส่งกลิ่นเหม็น ทำให้กินต่อเมนูนั้นไม่ได้ รู้สึกผิดหวัง พนักงานเสิร์ฟห้องอาหารผู้ชายพูดไทยไม่รู้เรื่อง พูดวกวน จนลูกค้างงไปหมด แถม</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -804,13 +808,9 @@
         <v>171</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>ดี เคยมาพักหลายปีก่อนมากๆๆๆประมาณ 14-15 ปีได้ ที่นอนนุ่มเด้งดี ทีวีจอใหญ่มีเนตฟริค ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 5</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -910,7 +910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -923,7 +923,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>รอบนี้ (2026-08-31 06:45) มีรีวิวใหม่ 1 รายการ | เทียบรอบก่อน 2026-08-17 02:19</t>
+          <t>รอบนี้ (2026-09-07 05:46) มีรีวิวใหม่ 3 รายการ | เทียบรอบก่อน 2026-08-31 06:45</t>
         </is>
       </c>
     </row>
@@ -957,23 +957,69 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>RWK</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Imm Hotel Thapae</t>
+          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Teab</t>
+          <t>Doglover Animalsworld</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>ดี เคยมาพักหลายปีก่อนมากๆๆๆประมาณ 14-15 ปีได้ ที่นอนนุ่มเด้งดี ทีวีจอใหญ่มีเนตฟริค ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 5</t>
+          <t>ห้องอาหารใช้กุ้งเน่ามาทำอาหารสังเกตุจากกุ้งเก็บนานเริ่มดำ หางดำ เน่า และส่งกลิ่นเหม็น ทำให้กินต่อเมนูนั้นไม่ได้ รู้สึกผิดหวัง พนักงานเสิร์ฟห้องอาหารผู้ชายพูดไทยไม่รู้เรื่อง พูดวกวน จนลูกค้างงไปหมด แถมเสิร์ฟผิด 3 ครั้ง 1.เครื่องดื่มย้ำว่าขอเพิ่ม1แก้วเท่านั้น เสิร์ฟมา 2, ไข่คนเสิร์ฟเกินมา 1 เลยแจ้งว่าสั่งแค่ 1, ไข่ดาวสุกลูกค้าบอกว่า 1 จานขอเป็นระดับไข่สุก ดันเสิร์ แยกเพิ่มมาอีกจาน สปา scam ราคาสูงขึ้น 2 เท่า ไม่เหมือนตามที่ตกลงและไม่แจ้งล่วงหน้า ลูกค้าจอง 1,500 บาท 90 นาที 2 ท่าน เมื่อไปถึงหน้างานขอเปลี่ยนเป็น 1 ชม. 800 บาท/ ท่าน สรุป บิลออกมา 3,100 บาท เลยถามว่า 60 นาที ไม่ใช่ 800? พนักงานนวดบอกว่าโปรแกรมต่างกัน แล้วทำไมไม่แจ้งลูกค้า?? สรุปตัดสินใจเช็คเอ้าออกก่อนเวลา ไม่อยู่ต่อ 2 คืน เสียความรู้สึกมากๆกับการบริการ  Prawns in our dish make we get sick because gone bad so not a fresh seafood. Hotel should not cook exp. food for the customers. Spa so scam we book 1 hr. but charges double price with a reason "different program " but not tell customer before. Staff in lobby and guard very nice service but in the restaurant a guy who is a waiter he can't talk Thai properly. He talk something mean opposite thing and so confused for us. Served wrong dish 3 times and something not asking he served extra so we need to pay more. Finally decided to check out at night (before time) can not suffer with their service so disappointed feel not comfortable. ห้องพัก: 1 บริการ: 1 สถานที่ตั้ง: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>RWK</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Jao pimpim</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>ไปพักมาตอนมีสอบที่สวนสุนันทา สะดวกดีค่ะ ไม่ห่างจากมหาวิทบาลัยมาก เดินไปประมาณ 900 เมตรนิด ๆ ห้องพักดี สะอาด กลิ่นหอม พนักงานบริการดีมาก ๆ ค่ะ ติดอย่างเดียวห้องที่พักเหมือนจะมีแมวส้มมาก่อกวน ร้องทั้งคืนเลยค่ะ ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>RWK</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Romain P</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>I had the pleasure of receiving a massage from Preeya, and the experience was absolutely outstanding.  Her professionalism, kindness, and attention to detail made the session incredibly relaxing. She quickly identified areas of tension and adjusted the treatment perfectly to my needs.  I travel a lot and have had massages in many countries, and this was truly one of the best experiences I have ever had.  Thank you, Preeya, for such a wonderful moment of relaxation and well-being. I will definitely come back and highly recommend her services.  ฉันมีโอกาสได้รับบริการนวดจากคุณปรียา และเป็นประสบการณ์ที่ยอดเยี่ยมมาก  เธอมีความเป็นมืออาชีพ ใส่ใจ และเป็นกันเอง ทำให้การนวดครั้งนี้ผ่อนคลายอย่างมาก เธอสามารถเข้าใจจุดที่มีความตึงเครียดของร่างกายและปรับการนวดให้เหมาะกับความต้องการของฉันได้อย่างสมบูรณ์แบบ  ฉันเดินทางมาหลายประเทศและเคยรับบริการนวดมามากมาย แต่นี่เป็นหนึ่งในประสบการณ์ที่ดีที่สุดที่เคยได้รับ  ขอบคุณคุณปรียาสำหรับช่วงเวลาแห่งความผ่อนคลายและความสุข ฉันจะกลับมาอีกแน่นอน และขอแนะนำเธอให้กับทุกคนอย่างยิ่ง ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
         </is>
       </c>
     </row>
@@ -988,7 +1034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1974,6 +2020,32 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>RWK</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Doglover Animalsworld</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>ห้องอาหารใช้กุ้งเน่ามาทำอาหารสังเกตุจากกุ้งเก็บนานเริ่มดำ หางดำ เน่า และส่งกลิ่นเหม็น ทำให้กินต่อเมนูนั้นไม่ได้ รู้สึกผิดหวัง พนักงานเสิร์ฟห้องอาหารผู้ชายพูดไทยไม่รู้เรื่อง พูดวกวน จนลูกค้างงไปหมด แถมเสิร์ฟผิด 3 ครั้ง 1.เครื่องดื่มย้ำว่าขอเพิ่ม1แก้วเท่านั้น เสิร์ฟมา 2, ไข่คนเสิร์ฟเกินมา 1 เลยแจ้งว่าสั่งแค่ 1, ไข่ดาวสุกลูกค้าบอกว่า 1 จานขอเป็นระดับไข่สุก ดันเสิร์ แยกเพิ่มมาอีกจาน สปา scam ราคาสูงขึ้น 2 เท่า ไม่เหมือนตามที่ตกลงและไม่แจ้งล่วงหน้า ลูกค้าจอง 1,500 บาท 90 นาที 2 ท่าน เมื่อไปถึงหน้างานขอเปลี่ยนเป็น 1 ชม. 800 บาท/ ท่าน สรุป บิลออกมา 3,100 บาท เลยถามว่า 60 นาที ไม่ใช่ 800? พนักงานนวดบอกว่าโปรแกรมต่างกัน แล้วทำไมไม่แจ้งลูกค้า?? สรุปตัดสินใจเช็คเอ้าออกก่อนเวลา ไม่อยู่ต่อ 2 คืน เสียความรู้สึกมากๆกับการบริการ  Prawns in our dish make we get sick because gone bad so not a fresh seafood. Hotel should not cook exp. food for the customers. Spa so scam we book 1 hr. but charges double price with a reason "different program " but not tell customer before. Staff in lobby and guard very nice service but in the restaurant a guy who is a waiter he can't talk Thai properly. He talk something mean opposite thing and so confused for us. Served wrong dish 3 times and something not asking he served extra so we need to pay more. Finally decided to check out at night (before time) can not suffer with their service so disappointed feel not comfortable. ห้องพัก: 1 บริการ: 1 สถานที่ตั้ง: 1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1985,7 +2057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3076,6 +3148,26 @@
         <v>1</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>RWK</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/report.xlsx
+++ b/report.xlsx
@@ -572,13 +572,9 @@
         <v>8</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>ห้องอาหารใช้กุ้งเน่ามาทำอาหารสังเกตุจากกุ้งเก็บนานเริ่มดำ หางดำ เน่า และส่งกลิ่นเหม็น ทำให้กินต่อเมนูนั้นไม่ได้ รู้สึกผิดหวัง พนักงานเสิร์ฟห้องอาหารผู้ชายพูดไทยไม่รู้เรื่อง พูดวกวน จนลูกค้างงไปหมด แถม</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -631,22 +627,26 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>ห้องก็โอเคครับไม่ได้เก่ามาก พนังงานให้ความช่วยเหลือดี สะอาดพอสมควร ห้องพักดี ทีวีใหญ่ มีเน็ตฟิก ยูทูป สมาร์ททีวี เตียงนุ่ม อุปกรณ์ในห้องครบครัน อาหารเช้าก็มีตัวเลือกมากพอสมควรครับ เป็นบุฟเฟต์ เลือกทาน</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>RWC</t>
+          <t>IMC</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Raweekanlaya Wellness Cuisine Resort</t>
+          <t>Imperial Chiang Mai Resort and Sport Club</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -656,11 +656,11 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
@@ -670,55 +670,59 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>IMC</t>
+          <t>IPL</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Imperial Chiang Mai Resort and Sport Club</t>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Chiang Mai</t>
+          <t>Phitsanulok</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>ห้องเก่าหน่อย แต่ถือว่าดูแลดี เตียงนอนสบาย บรรยากาศดีครับ ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 4</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>IPL</t>
+          <t>TSB</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Imperial Hotel Convention Center Phitsanulok</t>
+          <t>The Tantawan Hotel Surawong Bangkok</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Phitsanulok</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0</v>
@@ -728,12 +732,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>TSB</t>
+          <t>PLB</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>The Tantawan Hotel Surawong Bangkok</t>
+          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -747,27 +751,31 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>พนักงานผู้หญิงผมสั้นบริการไม่ดี ดูเพราะแต่ใช่น้ำเสียงข่มยิ้มแต่หน้าไม่รับก็ไม่ได้เนาะ  เสียเงินนะคะไม่ได้ขอนอนฟรี โดยรวมห้องก้ถทอว่าดีแต่จะค่อนข้างมืด และอีกอย่างบางห้องปิดยาก ล็อกแล้วก็เปิดเอง</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>PLB</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
+          <t>Imm Hotel Thapae</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Chiang Mai</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -776,7 +784,7 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>0</v>
@@ -786,12 +794,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>IUV</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Imm Hotel Thapae</t>
+          <t>Imperial Urban Villas Chiang Mai</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -805,7 +813,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>0</v>
@@ -815,12 +823,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>IUV</t>
+          <t>CHH</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Imperial Urban Villas Chiang Mai</t>
+          <t>CH Hotel Chiang Mai</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -830,11 +838,11 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
@@ -844,17 +852,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>CHH</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>CH Hotel Chiang Mai</t>
+          <t>Imperial Narathiwat Hotel</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Chiang Mai</t>
+          <t>Narathiwat</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -863,7 +871,7 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
@@ -873,26 +881,22 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>RWC</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Imperial Narathiwat Hotel</t>
+          <t>Raweekanlaya Wellness Cuisine Resort</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Narathiwat</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
-      </c>
+          <t>Chiang Mai</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="n">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>0</v>
@@ -923,7 +927,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>รอบนี้ (2026-09-07 05:46) มีรีวิวใหม่ 3 รายการ | เทียบรอบก่อน 2026-08-31 06:45</t>
+          <t>รอบนี้ (2026-09-14 05:53) มีรีวิวใหม่ 3 รายการ | เทียบรอบก่อน 2026-09-07 05:46</t>
         </is>
       </c>
     </row>
@@ -957,69 +961,69 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>RWK</t>
+          <t>PLB</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
+          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Doglover Animalsworld</t>
+          <t>เปรมวิกา Crystal</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>ห้องอาหารใช้กุ้งเน่ามาทำอาหารสังเกตุจากกุ้งเก็บนานเริ่มดำ หางดำ เน่า และส่งกลิ่นเหม็น ทำให้กินต่อเมนูนั้นไม่ได้ รู้สึกผิดหวัง พนักงานเสิร์ฟห้องอาหารผู้ชายพูดไทยไม่รู้เรื่อง พูดวกวน จนลูกค้างงไปหมด แถมเสิร์ฟผิด 3 ครั้ง 1.เครื่องดื่มย้ำว่าขอเพิ่ม1แก้วเท่านั้น เสิร์ฟมา 2, ไข่คนเสิร์ฟเกินมา 1 เลยแจ้งว่าสั่งแค่ 1, ไข่ดาวสุกลูกค้าบอกว่า 1 จานขอเป็นระดับไข่สุก ดันเสิร์ แยกเพิ่มมาอีกจาน สปา scam ราคาสูงขึ้น 2 เท่า ไม่เหมือนตามที่ตกลงและไม่แจ้งล่วงหน้า ลูกค้าจอง 1,500 บาท 90 นาที 2 ท่าน เมื่อไปถึงหน้างานขอเปลี่ยนเป็น 1 ชม. 800 บาท/ ท่าน สรุป บิลออกมา 3,100 บาท เลยถามว่า 60 นาที ไม่ใช่ 800? พนักงานนวดบอกว่าโปรแกรมต่างกัน แล้วทำไมไม่แจ้งลูกค้า?? สรุปตัดสินใจเช็คเอ้าออกก่อนเวลา ไม่อยู่ต่อ 2 คืน เสียความรู้สึกมากๆกับการบริการ  Prawns in our dish make we get sick because gone bad so not a fresh seafood. Hotel should not cook exp. food for the customers. Spa so scam we book 1 hr. but charges double price with a reason "different program " but not tell customer before. Staff in lobby and guard very nice service but in the restaurant a guy who is a waiter he can't talk Thai properly. He talk something mean opposite thing and so confused for us. Served wrong dish 3 times and something not asking he served extra so we need to pay more. Finally decided to check out at night (before time) can not suffer with their service so disappointed feel not comfortable. ห้องพัก: 1 บริการ: 1 สถานที่ตั้ง: 1</t>
+          <t>พนักงานผู้หญิงผมสั้นบริการไม่ดี ดูเพราะแต่ใช่น้ำเสียงข่มยิ้มแต่หน้าไม่รับก็ไม่ได้เนาะ  เสียเงินนะคะไม่ได้ขอนอนฟรี โดยรวมห้องก้ถทอว่าดีแต่จะค่อนข้างมืด และอีกอย่างบางห้องปิดยาก ล็อกแล้วก็เปิดเอง</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>RWK</t>
+          <t>IPL</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Jao pimpim</t>
+          <t>PRUTTANON PACHARATHAKUL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>ไปพักมาตอนมีสอบที่สวนสุนันทา สะดวกดีค่ะ ไม่ห่างจากมหาวิทบาลัยมาก เดินไปประมาณ 900 เมตรนิด ๆ ห้องพักดี สะอาด กลิ่นหอม พนักงานบริการดีมาก ๆ ค่ะ ติดอย่างเดียวห้องที่พักเหมือนจะมีแมวส้มมาก่อกวน ร้องทั้งคืนเลยค่ะ ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+          <t>ห้องเก่าหน่อย แต่ถือว่าดูแลดี เตียงนอนสบาย บรรยากาศดีครับ ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>RWK</t>
+          <t>IMK</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
+          <t>Imperial Hotel Convention Center Korat</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Romain P</t>
+          <t>อนวัช แจ่มจันทร์</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>I had the pleasure of receiving a massage from Preeya, and the experience was absolutely outstanding.  Her professionalism, kindness, and attention to detail made the session incredibly relaxing. She quickly identified areas of tension and adjusted the treatment perfectly to my needs.  I travel a lot and have had massages in many countries, and this was truly one of the best experiences I have ever had.  Thank you, Preeya, for such a wonderful moment of relaxation and well-being. I will definitely come back and highly recommend her services.  ฉันมีโอกาสได้รับบริการนวดจากคุณปรียา และเป็นประสบการณ์ที่ยอดเยี่ยมมาก  เธอมีความเป็นมืออาชีพ ใส่ใจ และเป็นกันเอง ทำให้การนวดครั้งนี้ผ่อนคลายอย่างมาก เธอสามารถเข้าใจจุดที่มีความตึงเครียดของร่างกายและปรับการนวดให้เหมาะกับความต้องการของฉันได้อย่างสมบูรณ์แบบ  ฉันเดินทางมาหลายประเทศและเคยรับบริการนวดมามากมาย แต่นี่เป็นหนึ่งในประสบการณ์ที่ดีที่สุดที่เคยได้รับ  ขอบคุณคุณปรียาสำหรับช่วงเวลาแห่งความผ่อนคลายและความสุข ฉันจะกลับมาอีกแน่นอน และขอแนะนำเธอให้กับทุกคนอย่างยิ่ง ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5</t>
+          <t>ห้องก็โอเคครับไม่ได้เก่ามาก พนังงานให้ความช่วยเหลือดี สะอาดพอสมควร ห้องพักดี ทีวีใหญ่ มีเน็ตฟิก ยูทูป สมาร์ททีวี เตียงนุ่ม อุปกรณ์ในห้องครบครัน อาหารเช้าก็มีตัวเลือกมากพอสมควรครับ เป็นบุฟเฟต์ เลือกทานได้ตามสบาย โดยรวมถือว่าดีครับ ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ห้องพัก อุปกรณ์ครบครัน เตียงนุ่ม แอร์เย็น กิจกรรมในบริเวณใกล้เคียง ตลาดนัด ความปลอดภัย ดีครับ มี รปภ ความสามารถเดินได้ เดินได้มีแหล่งของกินเยอะพอสมควร อาหารและเครื่องดื่ม มีบริการจากทางโรงแรม รายละเอียดที่น่าสนใจ เป็นอีกหนึ่งตัวเลือกที่สามารถมาพักได้ราคาก็ไม่ได้สูงมาก ไฮไลต์ของโรงแรม หรูหรา และ คุ้มค่า</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3168,6 +3172,66 @@
         <v>3</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>IMK</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Korat</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>IPL</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>PLB</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/report.xlsx
+++ b/report.xlsx
@@ -521,17 +521,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>IBC</t>
+          <t>RWC</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
+          <t>Raweekanlaya Wellness Cuisine Resort</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Petchaburi</t>
+          <t>Chiang Mai</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
@@ -630,37 +630,33 @@
         <v>173</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>ห้องก็โอเคครับไม่ได้เก่ามาก พนังงานให้ความช่วยเหลือดี สะอาดพอสมควร ห้องพักดี ทีวีใหญ่ มีเน็ตฟิก ยูทูป สมาร์ททีวี เตียงนุ่ม อุปกรณ์ในห้องครบครัน อาหารเช้าก็มีตัวเลือกมากพอสมควรครับ เป็นบุฟเฟต์ เลือกทาน</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>IMC</t>
+          <t>IBC</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Imperial Chiang Mai Resort and Sport Club</t>
+          <t>Imperial Beachfront Resort Cha-am</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Chiang Mai</t>
+          <t>Petchaburi</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>173</v>
+        <v>30</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
@@ -670,74 +666,74 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>IPL</t>
+          <t>IMC</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Imperial Hotel Convention Center Phitsanulok</t>
+          <t>Imperial Chiang Mai Resort and Sport Club</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Phitsanulok</t>
+          <t>Chiang Mai</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>ห้องเก่าหน่อย แต่ถือว่าดูแลดี เตียงนอนสบาย บรรยากาศดีครับ ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 4</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TSB</t>
+          <t>IPL</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>The Tantawan Hotel Surawong Bangkok</t>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Phitsanulok</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>บรรยากาศดี สระว่ายน้ำกว้างเงียบสงบไม่พลุกพล่าน ชอบที่กว้างใหญ่สะอาดด้วยค่ะ อาหารเช้าอร่อยมีให้เลือกหลากหลาย พนักงานบริการดี เตียงนุ่ม💕 ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว คู่รัก ห้องพัก: 5 บริการ:</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>PLB</t>
+          <t>TSB</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
+          <t>The Tantawan Hotel Surawong Bangkok</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -751,31 +747,27 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>พนักงานผู้หญิงผมสั้นบริการไม่ดี ดูเพราะแต่ใช่น้ำเสียงข่มยิ้มแต่หน้าไม่รับก็ไม่ได้เนาะ  เสียเงินนะคะไม่ได้ขอนอนฟรี โดยรวมห้องก้ถทอว่าดีแต่จะค่อนข้างมืด และอีกอย่างบางห้องปิดยาก ล็อกแล้วก็เปิดเอง</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>PLB</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Imm Hotel Thapae</t>
+          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Chiang Mai</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -784,22 +776,26 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>เขาวัดรร. 4 ดาวจากตรงไหนหรอ ห้องพัก: 3 บริการ: 4 สถานที่ตั้ง: 1</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>IUV</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Imperial Urban Villas Chiang Mai</t>
+          <t>Imm Hotel Thapae</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -813,22 +809,26 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>มาเที่ยวเชียงใหม่ ลองกดจองครั้งแรกคือมาพักวันอาทิตย์ ที่เลือกเพราะใกล้ถนนคนเดิน มีที่จอดรถ ทีวีเป็นsmart TVด้วย ใกล้แหล่งของกิน สะดวกมากๆๆ ถูกใจค่ะ กลับมาพักอีกครั้ง ได้อัพเกรดห้องด้วย ห้องใหญ่ น้องพน</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>CHH</t>
+          <t>IUV</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CH Hotel Chiang Mai</t>
+          <t>Imperial Urban Villas Chiang Mai</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -838,11 +838,11 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
@@ -852,17 +852,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>CHH</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Imperial Narathiwat Hotel</t>
+          <t>CH Hotel Chiang Mai</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Narathiwat</t>
+          <t>Chiang Mai</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -871,7 +871,7 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>0</v>
@@ -881,27 +881,35 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>RWC</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Raweekanlaya Wellness Cuisine Resort</t>
+          <t>Imperial Narathiwat Hotel</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Chiang Mai</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr"/>
+          <t>Narathiwat</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="n">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>ถึงจะเก่า แต่แอร์เย็นช่ำ ก็โอเคเลย ห้องสะอาดเรียบร้อย ห้องพัก: 3 บริการ: 3 สถานที่ตั้ง: 3</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -914,7 +922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -927,7 +935,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>รอบนี้ (2026-09-14 05:53) มีรีวิวใหม่ 3 รายการ | เทียบรอบก่อน 2026-09-07 05:46</t>
+          <t>รอบนี้ (2026-09-21 05:58) มีรีวิวใหม่ 5 รายการ | เทียบรอบก่อน 2026-09-14 05:53</t>
         </is>
       </c>
     </row>
@@ -971,59 +979,105 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>เปรมวิกา Crystal</t>
+          <t>Palita zax007</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>พนักงานผู้หญิงผมสั้นบริการไม่ดี ดูเพราะแต่ใช่น้ำเสียงข่มยิ้มแต่หน้าไม่รับก็ไม่ได้เนาะ  เสียเงินนะคะไม่ได้ขอนอนฟรี โดยรวมห้องก้ถทอว่าดีแต่จะค่อนข้างมืด และอีกอย่างบางห้องปิดยาก ล็อกแล้วก็เปิดเอง</t>
+          <t>เขาวัดรร. 4 ดาวจากตรงไหนหรอ ห้องพัก: 3 บริการ: 4 สถานที่ตั้ง: 1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>IPL</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Imperial Hotel Convention Center Phitsanulok</t>
+          <t>Imm Hotel Thapae</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>PRUTTANON PACHARATHAKUL</t>
+          <t>Ann Tiicha</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>ห้องเก่าหน่อย แต่ถือว่าดูแลดี เตียงนอนสบาย บรรยากาศดีครับ ห้องพัก: 4 บริการ: 4 สถานที่ตั้ง: 4</t>
+          <t>มาเที่ยวเชียงใหม่ ลองกดจองครั้งแรกคือมาพักวันอาทิตย์ ที่เลือกเพราะใกล้ถนนคนเดิน มีที่จอดรถ ทีวีเป็นsmart TVด้วย ใกล้แหล่งของกิน สะดวกมากๆๆ ถูกใจค่ะ กลับมาพักอีกครั้ง ได้อัพเกรดห้องด้วย ห้องใหญ่ น้องพนักงานหน้าฟร้อน น่ารัก พูดจาสุภาพ แนะนำเลย 👍 ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ความสบายของเตียง สบายมาก</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>IMK</t>
+          <t>IPL</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Imperial Hotel Convention Center Korat</t>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>อนวัช แจ่มจันทร์</t>
+          <t>prattana boonbaramee</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>ห้องก็โอเคครับไม่ได้เก่ามาก พนังงานให้ความช่วยเหลือดี สะอาดพอสมควร ห้องพักดี ทีวีใหญ่ มีเน็ตฟิก ยูทูป สมาร์ททีวี เตียงนุ่ม อุปกรณ์ในห้องครบครัน อาหารเช้าก็มีตัวเลือกมากพอสมควรครับ เป็นบุฟเฟต์ เลือกทานได้ตามสบาย โดยรวมถือว่าดีครับ ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ห้องพัก อุปกรณ์ครบครัน เตียงนุ่ม แอร์เย็น กิจกรรมในบริเวณใกล้เคียง ตลาดนัด ความปลอดภัย ดีครับ มี รปภ ความสามารถเดินได้ เดินได้มีแหล่งของกินเยอะพอสมควร อาหารและเครื่องดื่ม มีบริการจากทางโรงแรม รายละเอียดที่น่าสนใจ เป็นอีกหนึ่งตัวเลือกที่สามารถมาพักได้ราคาก็ไม่ได้สูงมาก ไฮไลต์ของโรงแรม หรูหรา และ คุ้มค่า</t>
+          <t>บรรยากาศดี สระว่ายน้ำกว้างเงียบสงบไม่พลุกพล่าน ชอบที่กว้างใหญ่สะอาดด้วยค่ะ อาหารเช้าอร่อยมีให้เลือกหลากหลาย พนักงานบริการดี เตียงนุ่ม💕 ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว คู่รัก ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม หรูหรา วิวสวย โรแมนติก เงียบสงบ เหมาะสำหรับเด็ก และ คุ้มค่า</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>IPL</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>noi duang</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>ห้องอย่างเก่า น้ำไหลอ่อน ห้องน้ำโบราน แอร์เสียงดัง ที่นอนพอรับได้ ถ้าเลือกได้ในราคาขนาดนี้ เลือกที่ใหม่ๆ ดีกว่าครับ เสียชื่อ รร.ดีๆ แต่ไม่พัฒนา ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 1 บริการ: 4 สถานที่ตั้ง: 4 ห้องพัก เก่า แอรดัง น้ำไม่ไหล</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Narathiwat Hotel</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>เอก พลอยสีขํา (ลุงเอก)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>ถึงจะเก่า แต่แอร์เย็นช่ำ ก็โอเคเลย ห้องสะอาดเรียบร้อย ห้องพัก: 3 บริการ: 3 สถานที่ตั้ง: 3</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3232,6 +3286,86 @@
         <v>1</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>Imperial Narathiwat Hotel</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>IPL</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>Imm Hotel Thapae</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>PLB</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/report.xlsx
+++ b/report.xlsx
@@ -521,17 +521,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>RWC</t>
+          <t>RWK</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Raweekanlaya Wellness Cuisine Resort</t>
+          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Chiang Mai</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>160</v>
+        <v>8</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
@@ -550,26 +550,26 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>RWK</t>
+          <t>IRH</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
+          <t>Imperial River House Resort</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Chiang Rai</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>8</v>
+        <v>164</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
@@ -579,26 +579,26 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>IRH</t>
+          <t>IMK</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Imperial River House Resort</t>
+          <t>Imperial Hotel Convention Center Korat</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Chiang Rai</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
@@ -608,17 +608,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>IMK</t>
+          <t>IBC</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Imperial Hotel Convention Center Korat</t>
+          <t>Imperial Beachfront Resort Cha-am</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Petchaburi</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>173</v>
+        <v>30</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
@@ -637,26 +637,26 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>IBC</t>
+          <t>IMC</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
+          <t>Imperial Chiang Mai Resort and Sport Club</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Petchaburi</t>
+          <t>Chiang Mai</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>30</v>
+        <v>173</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
@@ -666,74 +666,74 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>IMC</t>
+          <t>IPL</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Imperial Chiang Mai Resort and Sport Club</t>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Chiang Mai</t>
+          <t>Phitsanulok</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>บรรยากาศดี สระว่ายน้ำกว้างเงียบสงบไม่พลุกพล่าน ชอบที่กว้างใหญ่สะอาดด้วยค่ะ อาหารเช้าอร่อยมีให้เลือกหลากหลาย พนักงานบริการดี เตียงนุ่ม💕 ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว คู่รัก ห้องพัก: 5 บริการ:</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>IPL</t>
+          <t>TSB</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Imperial Hotel Convention Center Phitsanulok</t>
+          <t>The Tantawan Hotel Surawong Bangkok</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Phitsanulok</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>บรรยากาศดี สระว่ายน้ำกว้างเงียบสงบไม่พลุกพล่าน ชอบที่กว้างใหญ่สะอาดด้วยค่ะ อาหารเช้าอร่อยมีให้เลือกหลากหลาย พนักงานบริการดี เตียงนุ่ม💕 ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว คู่รัก ห้องพัก: 5 บริการ:</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>TSB</t>
+          <t>PLB</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>The Tantawan Hotel Surawong Bangkok</t>
+          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -747,27 +747,31 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>เขาวัดรร. 4 ดาวจากตรงไหนหรอ ห้องพัก: 3 บริการ: 4 สถานที่ตั้ง: 1</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>PLB</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
+          <t>Imm Hotel Thapae</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Chiang Mai</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -783,19 +787,19 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>เขาวัดรร. 4 ดาวจากตรงไหนหรอ ห้องพัก: 3 บริการ: 4 สถานที่ตั้ง: 1</t>
+          <t>มาเที่ยวเชียงใหม่ ลองกดจองครั้งแรกคือมาพักวันอาทิตย์ ที่เลือกเพราะใกล้ถนนคนเดิน มีที่จอดรถ ทีวีเป็นsmart TVด้วย ใกล้แหล่งของกิน สะดวกมากๆๆ ถูกใจค่ะ กลับมาพักอีกครั้ง ได้อัพเกรดห้องด้วย ห้องใหญ่ น้องพน</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>IUV</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Imm Hotel Thapae</t>
+          <t>Imperial Urban Villas Chiang Mai</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -809,26 +813,22 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>มาเที่ยวเชียงใหม่ ลองกดจองครั้งแรกคือมาพักวันอาทิตย์ ที่เลือกเพราะใกล้ถนนคนเดิน มีที่จอดรถ ทีวีเป็นsmart TVด้วย ใกล้แหล่งของกิน สะดวกมากๆๆ ถูกใจค่ะ กลับมาพักอีกครั้ง ได้อัพเกรดห้องด้วย ห้องใหญ่ น้องพน</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>IUV</t>
+          <t>CHH</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Imperial Urban Villas Chiang Mai</t>
+          <t>CH Hotel Chiang Mai</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -838,11 +838,11 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>0</v>
@@ -852,17 +852,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>CHH</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>CH Hotel Chiang Mai</t>
+          <t>Imperial Narathiwat Hotel</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Chiang Mai</t>
+          <t>Narathiwat</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -871,45 +871,41 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>ถึงจะเก่า แต่แอร์เย็นช่ำ ก็โอเคเลย ห้องสะอาดเรียบร้อย ห้องพัก: 3 บริการ: 3 สถานที่ตั้ง: 3</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>RWC</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Imperial Narathiwat Hotel</t>
+          <t>Raweekanlaya Wellness Cuisine Resort</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Narathiwat</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
-      </c>
+          <t>Chiang Mai</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="2" t="n">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>ถึงจะเก่า แต่แอร์เย็นช่ำ ก็โอเคเลย ห้องสะอาดเรียบร้อย ห้องพัก: 3 บริการ: 3 สถานที่ตั้ง: 3</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/report.xlsx
+++ b/report.xlsx
@@ -521,17 +521,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>RWK</t>
+          <t>RWC</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
+          <t>Raweekanlaya Wellness Cuisine Resort</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Chiang Mai</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>8</v>
+        <v>160</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
@@ -550,26 +550,26 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>IRH</t>
+          <t>RWK</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Imperial River House Resort</t>
+          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Chiang Rai</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>164</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
@@ -579,26 +579,26 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>IMK</t>
+          <t>IRH</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Imperial Hotel Convention Center Korat</t>
+          <t>Imperial River House Resort</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Chiang Rai</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>0</v>
@@ -608,17 +608,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>IBC</t>
+          <t>IMK</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Imperial Beachfront Resort Cha-am</t>
+          <t>Imperial Hotel Convention Center Korat</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Petchaburi</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>30</v>
+        <v>173</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
@@ -637,26 +637,26 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>IMC</t>
+          <t>IBC</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Imperial Chiang Mai Resort and Sport Club</t>
+          <t>Imperial Beachfront Resort Cha-am</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Chiang Mai</t>
+          <t>Petchaburi</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>173</v>
+        <v>30</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>0</v>
@@ -666,74 +666,74 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>IPL</t>
+          <t>IMC</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Imperial Hotel Convention Center Phitsanulok</t>
+          <t>Imperial Chiang Mai Resort and Sport Club</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Phitsanulok</t>
+          <t>Chiang Mai</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>บรรยากาศดี สระว่ายน้ำกว้างเงียบสงบไม่พลุกพล่าน ชอบที่กว้างใหญ่สะอาดด้วยค่ะ อาหารเช้าอร่อยมีให้เลือกหลากหลาย พนักงานบริการดี เตียงนุ่ม💕 ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว คู่รัก ห้องพัก: 5 บริการ:</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TSB</t>
+          <t>IPL</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>The Tantawan Hotel Surawong Bangkok</t>
+          <t>Imperial Hotel Convention Center Phitsanulok</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Bangkok</t>
+          <t>Phitsanulok</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>บรรยากาศดี สระว่ายน้ำกว้างเงียบสงบไม่พลุกพล่าน ชอบที่กว้างใหญ่สะอาดด้วยค่ะ อาหารเช้าอร่อยมีให้เลือกหลากหลาย พนักงานบริการดี เตียงนุ่ม💕 ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว คู่รัก ห้องพัก: 5 บริการ:</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>PLB</t>
+          <t>TSB</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
+          <t>The Tantawan Hotel Surawong Bangkok</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -747,16 +747,12 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>เขาวัดรร. 4 ดาวจากตรงไหนหรอ ห้องพัก: 3 บริการ: 4 สถานที่ตั้ง: 1</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -823,17 +819,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>CHH</t>
+          <t>PLB</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CH Hotel Chiang Mai</t>
+          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Chiang Mai</t>
+          <t>Bangkok</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -842,27 +838,31 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>เขาวัดรร. 4 ดาวจากตรงไหนหรอ ห้องพัก: 3 บริการ: 4 สถานที่ตั้ง: 1</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>CHH</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Imperial Narathiwat Hotel</t>
+          <t>CH Hotel Chiang Mai</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Narathiwat</t>
+          <t>Chiang Mai</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -871,41 +871,45 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>ถึงจะเก่า แต่แอร์เย็นช่ำ ก็โอเคเลย ห้องสะอาดเรียบร้อย ห้องพัก: 3 บริการ: 3 สถานที่ตั้ง: 3</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>RWC</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Raweekanlaya Wellness Cuisine Resort</t>
+          <t>Imperial Narathiwat Hotel</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Chiang Mai</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr"/>
+          <t>Narathiwat</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
       <c r="E14" s="2" t="n">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>ถึงจะเก่า แต่แอร์เย็นช่ำ ก็โอเคเลย ห้องสะอาดเรียบร้อย ห้องพัก: 3 บริการ: 3 สถานที่ตั้ง: 3</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/report.xlsx
+++ b/report.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -569,12 +569,16 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>ห้องอาหารใช้กุ้งเน่ามาทำอาหารสังเกตุจากกุ้งเก็บนานเริ่มดำ หางดำ เน่า และส่งกลิ่นเหม็น ทำให้กินต่อเมนูนั้นไม่ได้ รู้สึกผิดหวัง พนักงานเสิร์ฟห้องอาหารผู้ชายพูดไทยไม่รู้เรื่อง พูดวกวน จนลูกค้างงไปหมด แถม</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -717,13 +721,9 @@
         <v>179</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>บรรยากาศดี สระว่ายน้ำกว้างเงียบสงบไม่พลุกพล่าน ชอบที่กว้างใหญ่สะอาดด้วยค่ะ อาหารเช้าอร่อยมีให้เลือกหลากหลาย พนักงานบริการดี เตียงนุ่ม💕 ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว คู่รัก ห้องพัก: 5 บริการ:</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -779,13 +779,9 @@
         <v>172</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>มาเที่ยวเชียงใหม่ ลองกดจองครั้งแรกคือมาพักวันอาทิตย์ ที่เลือกเพราะใกล้ถนนคนเดิน มีที่จอดรถ ทีวีเป็นsmart TVด้วย ใกล้แหล่งของกิน สะดวกมากๆๆ ถูกใจค่ะ กลับมาพักอีกครั้ง ได้อัพเกรดห้องด้วย ห้องใหญ่ น้องพน</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -841,13 +837,9 @@
         <v>172</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>เขาวัดรร. 4 ดาวจากตรงไหนหรอ ห้องพัก: 3 บริการ: 4 สถานที่ตั้ง: 1</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -903,13 +895,9 @@
         <v>172</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>ถึงจะเก่า แต่แอร์เย็นช่ำ ก็โอเคเลย ห้องสะอาดเรียบร้อย ห้องพัก: 3 บริการ: 3 สถานที่ตั้ง: 3</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -922,7 +910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -935,7 +923,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>รอบนี้ (2026-09-21 05:58) มีรีวิวใหม่ 5 รายการ | เทียบรอบก่อน 2026-09-14 05:53</t>
+          <t>รอบนี้ (2026-10-12 07:01) มีรีวิวใหม่ 1 รายการ | เทียบรอบก่อน 2026-09-21 05:58</t>
         </is>
       </c>
     </row>
@@ -969,115 +957,23 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>PLB</t>
+          <t>RWK</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Imm Hotel Ladprao Bangkapi Bangkok</t>
+          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Palita zax007</t>
+          <t>เจริญรัตน์</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>เขาวัดรร. 4 ดาวจากตรงไหนหรอ ห้องพัก: 3 บริการ: 4 สถานที่ตั้ง: 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>ITC</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Imm Hotel Thapae</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Ann Tiicha</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>มาเที่ยวเชียงใหม่ ลองกดจองครั้งแรกคือมาพักวันอาทิตย์ ที่เลือกเพราะใกล้ถนนคนเดิน มีที่จอดรถ ทีวีเป็นsmart TVด้วย ใกล้แหล่งของกิน สะดวกมากๆๆ ถูกใจค่ะ กลับมาพักอีกครั้ง ได้อัพเกรดห้องด้วย ห้องใหญ่ น้องพนักงานหน้าฟร้อน น่ารัก พูดจาสุภาพ แนะนำเลย 👍 ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ความสบายของเตียง สบายมาก</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>IPL</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Hotel Convention Center Phitsanulok</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>prattana boonbaramee</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>บรรยากาศดี สระว่ายน้ำกว้างเงียบสงบไม่พลุกพล่าน ชอบที่กว้างใหญ่สะอาดด้วยค่ะ อาหารเช้าอร่อยมีให้เลือกหลากหลาย พนักงานบริการดี เตียงนุ่ม💕 ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว คู่รัก ห้องพัก: 5 บริการ: 5 สถานที่ตั้ง: 5 ไฮไลต์ของโรงแรม หรูหรา วิวสวย โรแมนติก เงียบสงบ เหมาะสำหรับเด็ก และ คุ้มค่า</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>IPL</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Hotel Convention Center Phitsanulok</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>noi duang</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>ห้องอย่างเก่า น้ำไหลอ่อน ห้องน้ำโบราน แอร์เสียงดัง ที่นอนพอรับได้ ถ้าเลือกได้ในราคาขนาดนี้ เลือกที่ใหม่ๆ ดีกว่าครับ เสียชื่อ รร.ดีๆ แต่ไม่พัฒนา ประเภทการเดินทาง ธุรกิจ กลุ่มท่องเที่ยว เพื่อน ห้องพัก: 1 บริการ: 4 สถานที่ตั้ง: 4 ห้องพัก เก่า แอรดัง น้ำไม่ไหล</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Imperial Narathiwat Hotel</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>เอก พลอยสีขํา (ลุงเอก)</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>ถึงจะเก่า แต่แอร์เย็นช่ำ ก็โอเคเลย ห้องสะอาดเรียบร้อย ห้องพัก: 3 บริการ: 3 สถานที่ตั้ง: 3</t>
+          <t>ห้องอาหารใช้กุ้งเน่ามาทำอาหารสังเกตุจากกุ้งเก็บนานเริ่มดำ หางดำ เน่า และส่งกลิ่นเหม็น ทำให้กินต่อเมนูนั้นไม่ได้ รู้สึกผิดหวัง พนักงานเสิร์ฟห้องอาหารผู้ชายพูดไทยไม่รู้เรื่อง พูดวกวน จนลูกค้างงไปหมด แถมเสิร์ฟผิด 3 ครั้ง 1.เครื่องดื่มย้ำว่าขอเพิ่ม1แก้วเท่านั้น เสิร์ฟมา 2, ไข่คนเสิร์ฟเกินมา 1 เลยแจ้งว่าสั่งแค่ 1, ไข่ดาวสุกลูกค้าบอกว่า 1 จานขอเป็นระดับไข่สุก ดันเสิร์ แยกเพิ่มมาอีกจาน สปา scam ราคาสูงขึ้น 2 เท่า ไม่เหมือนตามที่ตกลงและไม่แจ้งล่วงหน้า ลูกค้าจอง 1,500 บาท 90 นาที 2 ท่าน เมื่อไปถึงหน้างานขอเปลี่ยนเป็น 1 ชม. 800 บาท/ ท่าน สรุป บิลออกมา 3,100 บาท เลยถามว่า 60 นาที ไม่ใช่ 800? พนักงานนวดบอกว่าโปรแกรมต่างกัน แล้วทำไมไม่แจ้งลูกค้า?? สรุปตัดสินใจเช็คเอ้าออกก่อนเวลา ไม่อยู่ต่อ 2 คืน เสียความรู้สึกมากๆกับการบริการ  Prawns in our dish make we get sick because gone bad so not a fresh seafood. Hotel should not cook exp. food for the customers. Spa so scam we book 1 hr. but charges double price with a reason "different program " but not tell customer before. Staff in lobby and guard very nice service but in the restaurant a guy who is a waiter he can't talk Thai properly. He talk something mean opposite thing and so confused for us. Served wrong dish 3 times and something not asking he served extra so we need to pay more. Finally decided to check out at night (before time) can not suffer with their service so disappointed feel not comfortable. ห้องพัก: 1 บริการ: 1 สถานที่ตั้ง: 1</t>
         </is>
       </c>
     </row>
@@ -1092,7 +988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2104,6 +2000,32 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>RWK</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>เจริญรัตน์</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>ห้องอาหารใช้กุ้งเน่ามาทำอาหารสังเกตุจากกุ้งเก็บนานเริ่มดำ หางดำ เน่า และส่งกลิ่นเหม็น ทำให้กินต่อเมนูนั้นไม่ได้ รู้สึกผิดหวัง พนักงานเสิร์ฟห้องอาหารผู้ชายพูดไทยไม่รู้เรื่อง พูดวกวน จนลูกค้างงไปหมด แถมเสิร์ฟผิด 3 ครั้ง 1.เครื่องดื่มย้ำว่าขอเพิ่ม1แก้วเท่านั้น เสิร์ฟมา 2, ไข่คนเสิร์ฟเกินมา 1 เลยแจ้งว่าสั่งแค่ 1, ไข่ดาวสุกลูกค้าบอกว่า 1 จานขอเป็นระดับไข่สุก ดันเสิร์ แยกเพิ่มมาอีกจาน สปา scam ราคาสูงขึ้น 2 เท่า ไม่เหมือนตามที่ตกลงและไม่แจ้งล่วงหน้า ลูกค้าจอง 1,500 บาท 90 นาที 2 ท่าน เมื่อไปถึงหน้างานขอเปลี่ยนเป็น 1 ชม. 800 บาท/ ท่าน สรุป บิลออกมา 3,100 บาท เลยถามว่า 60 นาที ไม่ใช่ 800? พนักงานนวดบอกว่าโปรแกรมต่างกัน แล้วทำไมไม่แจ้งลูกค้า?? สรุปตัดสินใจเช็คเอ้าออกก่อนเวลา ไม่อยู่ต่อ 2 คืน เสียความรู้สึกมากๆกับการบริการ  Prawns in our dish make we get sick because gone bad so not a fresh seafood. Hotel should not cook exp. food for the customers. Spa so scam we book 1 hr. but charges double price with a reason "different program " but not tell customer before. Staff in lobby and guard very nice service but in the restaurant a guy who is a waiter he can't talk Thai properly. He talk something mean opposite thing and so confused for us. Served wrong dish 3 times and something not asking he served extra so we need to pay more. Finally decided to check out at night (before time) can not suffer with their service so disappointed feel not comfortable. ห้องพัก: 1 บริการ: 1 สถานที่ตั้ง: 1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2115,7 +2037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3366,6 +3288,26 @@
         <v>1</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>RWK</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>The Raweekanlaya Bangkok Wellness Cuisine resort</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
